--- a/research/traditional_assets/database/data/namibia/namibia_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/namibia/namibia_beverage_alcoholic.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1172620337865825</v>
+        <v>0.1169173952784655</v>
       </c>
       <c r="C2">
-        <v>358.6828471386086</v>
+        <v>356.8213543406975</v>
       </c>
       <c r="D2">
-        <v>355.0328471386086</v>
+        <v>356.7533543406975</v>
       </c>
       <c r="E2">
-        <v>-36.6</v>
+        <v>-33.018</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.582000000000001</v>
       </c>
       <c r="G2">
         <v>3.65</v>
@@ -1451,28 +1451,28 @@
         <v>25.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1801746</v>
       </c>
       <c r="N2">
-        <v>25.5</v>
+        <v>25.3198254</v>
       </c>
       <c r="O2">
-        <v>8.16</v>
+        <v>8.102344128</v>
       </c>
       <c r="P2">
-        <v>17.34</v>
+        <v>17.217481272</v>
       </c>
       <c r="Q2">
-        <v>25.84</v>
+        <v>25.717481272</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1172620337865825</v>
+        <v>0.1177528841196621</v>
       </c>
       <c r="T2">
-        <v>0.6910924838905985</v>
+        <v>0.6958393817597461</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>141.5293831649966</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1169173952784655</v>
+        <v>0.1165727567703484</v>
       </c>
       <c r="C3">
-        <v>356.8213543406975</v>
+        <v>354.9766180763</v>
       </c>
       <c r="D3">
-        <v>356.7533543406975</v>
+        <v>358.4906180763</v>
       </c>
       <c r="E3">
-        <v>-33.018</v>
+        <v>-29.436</v>
       </c>
       <c r="F3">
-        <v>3.582000000000001</v>
+        <v>7.164000000000001</v>
       </c>
       <c r="G3">
         <v>3.65</v>
@@ -1533,28 +1533,28 @@
         <v>25.5</v>
       </c>
       <c r="M3">
-        <v>0.1801746</v>
+        <v>0.3603492</v>
       </c>
       <c r="N3">
-        <v>25.3198254</v>
+        <v>25.1396508</v>
       </c>
       <c r="O3">
-        <v>8.102344128</v>
+        <v>8.044688255999999</v>
       </c>
       <c r="P3">
-        <v>17.217481272</v>
+        <v>17.094962544</v>
       </c>
       <c r="Q3">
-        <v>25.717481272</v>
+        <v>25.594962544</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1177528841196621</v>
+        <v>0.118253751806478</v>
       </c>
       <c r="T3">
-        <v>0.6958393817597461</v>
+        <v>0.7006831550956109</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>141.5293831649966</v>
+        <v>70.7646915824983</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1165727567703484</v>
+        <v>0.1162281182622313</v>
       </c>
       <c r="C4">
-        <v>354.9766180763</v>
+        <v>353.1488843386436</v>
       </c>
       <c r="D4">
-        <v>358.4906180763</v>
+        <v>360.2448843386436</v>
       </c>
       <c r="E4">
-        <v>-29.436</v>
+        <v>-25.854</v>
       </c>
       <c r="F4">
-        <v>7.164000000000001</v>
+        <v>10.746</v>
       </c>
       <c r="G4">
         <v>3.65</v>
@@ -1615,28 +1615,28 @@
         <v>25.5</v>
       </c>
       <c r="M4">
-        <v>0.3603492</v>
+        <v>0.5405238</v>
       </c>
       <c r="N4">
-        <v>25.1396508</v>
+        <v>24.9594762</v>
       </c>
       <c r="O4">
-        <v>8.044688255999999</v>
+        <v>7.987032384000001</v>
       </c>
       <c r="P4">
-        <v>17.094962544</v>
+        <v>16.972443816</v>
       </c>
       <c r="Q4">
-        <v>25.594962544</v>
+        <v>25.472443816</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.118253751806478</v>
+        <v>0.1187649466620942</v>
       </c>
       <c r="T4">
-        <v>0.7006831550956109</v>
+        <v>0.7056268000466482</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>70.7646915824983</v>
+        <v>47.17646105499887</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1162281182622313</v>
+        <v>0.1158834797541143</v>
       </c>
       <c r="C5">
-        <v>353.1488843386436</v>
+        <v>351.3384039596851</v>
       </c>
       <c r="D5">
-        <v>360.2448843386436</v>
+        <v>362.0164039596851</v>
       </c>
       <c r="E5">
-        <v>-25.854</v>
+        <v>-22.272</v>
       </c>
       <c r="F5">
-        <v>10.746</v>
+        <v>14.328</v>
       </c>
       <c r="G5">
         <v>3.65</v>
@@ -1697,28 +1697,28 @@
         <v>25.5</v>
       </c>
       <c r="M5">
-        <v>0.5405238</v>
+        <v>0.7206984000000001</v>
       </c>
       <c r="N5">
-        <v>24.9594762</v>
+        <v>24.7793016</v>
       </c>
       <c r="O5">
-        <v>7.987032384000001</v>
+        <v>7.929376512</v>
       </c>
       <c r="P5">
-        <v>16.972443816</v>
+        <v>16.849925088</v>
       </c>
       <c r="Q5">
-        <v>25.472443816</v>
+        <v>25.349925088</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1187649466620942</v>
+        <v>0.1192867914105357</v>
       </c>
       <c r="T5">
-        <v>0.7056268000466482</v>
+        <v>0.7106734376008321</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>47.17646105499887</v>
+        <v>35.38234579124915</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1158834797541143</v>
+        <v>0.1155388412459972</v>
       </c>
       <c r="C6">
-        <v>351.3384039596851</v>
+        <v>349.5454327296709</v>
       </c>
       <c r="D6">
-        <v>362.0164039596851</v>
+        <v>363.805432729671</v>
       </c>
       <c r="E6">
-        <v>-22.272</v>
+        <v>-18.69</v>
       </c>
       <c r="F6">
-        <v>14.328</v>
+        <v>17.91</v>
       </c>
       <c r="G6">
         <v>3.65</v>
@@ -1779,28 +1779,28 @@
         <v>25.5</v>
       </c>
       <c r="M6">
-        <v>0.7206984000000001</v>
+        <v>0.9008730000000001</v>
       </c>
       <c r="N6">
-        <v>24.7793016</v>
+        <v>24.599127</v>
       </c>
       <c r="O6">
-        <v>7.929376512</v>
+        <v>7.87172064</v>
       </c>
       <c r="P6">
-        <v>16.849925088</v>
+        <v>16.72740636</v>
       </c>
       <c r="Q6">
-        <v>25.349925088</v>
+        <v>25.22740636</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1192867914105357</v>
+        <v>0.1198196223642076</v>
       </c>
       <c r="T6">
-        <v>0.7106734376008321</v>
+        <v>0.7158263201561569</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>35.38234579124915</v>
+        <v>28.30587663299932</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1155388412459972</v>
+        <v>0.1151942027378801</v>
       </c>
       <c r="C7">
-        <v>349.5454327296709</v>
+        <v>347.7702315202621</v>
       </c>
       <c r="D7">
-        <v>363.805432729671</v>
+        <v>365.6122315202621</v>
       </c>
       <c r="E7">
-        <v>-18.69</v>
+        <v>-15.108</v>
       </c>
       <c r="F7">
-        <v>17.91</v>
+        <v>21.492</v>
       </c>
       <c r="G7">
         <v>3.65</v>
@@ -1861,28 +1861,28 @@
         <v>25.5</v>
       </c>
       <c r="M7">
-        <v>0.9008730000000001</v>
+        <v>1.0810476</v>
       </c>
       <c r="N7">
-        <v>24.599127</v>
+        <v>24.4189524</v>
       </c>
       <c r="O7">
-        <v>7.87172064</v>
+        <v>7.814064768</v>
       </c>
       <c r="P7">
-        <v>16.72740636</v>
+        <v>16.604887632</v>
       </c>
       <c r="Q7">
-        <v>25.22740636</v>
+        <v>25.104887632</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1198196223642076</v>
+        <v>0.120363790146681</v>
       </c>
       <c r="T7">
-        <v>0.7158263201561569</v>
+        <v>0.7210888385105308</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.30587663299932</v>
+        <v>23.58823052749943</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1151942027378801</v>
+        <v>0.1148495642297631</v>
       </c>
       <c r="C8">
-        <v>347.7702315202621</v>
+        <v>346.0130664113443</v>
       </c>
       <c r="D8">
-        <v>365.6122315202621</v>
+        <v>367.4370664113443</v>
       </c>
       <c r="E8">
-        <v>-15.108</v>
+        <v>-11.526</v>
       </c>
       <c r="F8">
-        <v>21.492</v>
+        <v>25.074</v>
       </c>
       <c r="G8">
         <v>3.65</v>
@@ -1943,28 +1943,28 @@
         <v>25.5</v>
       </c>
       <c r="M8">
-        <v>1.0810476</v>
+        <v>1.2612222</v>
       </c>
       <c r="N8">
-        <v>24.4189524</v>
+        <v>24.2387778</v>
       </c>
       <c r="O8">
-        <v>7.814064768</v>
+        <v>7.756408896000001</v>
       </c>
       <c r="P8">
-        <v>16.604887632</v>
+        <v>16.482368904</v>
       </c>
       <c r="Q8">
-        <v>25.104887632</v>
+        <v>24.982368904</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.120363790146681</v>
+        <v>0.1209196604621108</v>
       </c>
       <c r="T8">
-        <v>0.7210888385105308</v>
+        <v>0.7264645293026335</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.58823052749943</v>
+        <v>20.21848330928523</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1148495642297631</v>
+        <v>0.114504925721646</v>
       </c>
       <c r="C9">
-        <v>346.0130664113444</v>
+        <v>344.2742088216565</v>
       </c>
       <c r="D9">
-        <v>367.4370664113444</v>
+        <v>369.2802088216565</v>
       </c>
       <c r="E9">
-        <v>-11.526</v>
+        <v>-7.943999999999996</v>
       </c>
       <c r="F9">
-        <v>25.07400000000001</v>
+        <v>28.65600000000001</v>
       </c>
       <c r="G9">
         <v>3.65</v>
@@ -2025,28 +2025,28 @@
         <v>25.5</v>
       </c>
       <c r="M9">
-        <v>1.2612222</v>
+        <v>1.4413968</v>
       </c>
       <c r="N9">
-        <v>24.2387778</v>
+        <v>24.0586032</v>
       </c>
       <c r="O9">
-        <v>7.756408896000001</v>
+        <v>7.698753024</v>
       </c>
       <c r="P9">
-        <v>16.482368904</v>
+        <v>16.359850176</v>
       </c>
       <c r="Q9">
-        <v>24.982368904</v>
+        <v>24.859850176</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1209196604621108</v>
+        <v>0.1214876149148326</v>
       </c>
       <c r="T9">
-        <v>0.7264645293026335</v>
+        <v>0.7319570829380426</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.21848330928523</v>
+        <v>17.69117289562458</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.114504925721646</v>
+        <v>0.114160287213529</v>
       </c>
       <c r="C10">
-        <v>344.2742088216565</v>
+        <v>342.5539356433698</v>
       </c>
       <c r="D10">
-        <v>369.2802088216565</v>
+        <v>371.1419356433698</v>
       </c>
       <c r="E10">
-        <v>-7.943999999999996</v>
+        <v>-4.362000000000002</v>
       </c>
       <c r="F10">
-        <v>28.65600000000001</v>
+        <v>32.238</v>
       </c>
       <c r="G10">
         <v>3.65</v>
@@ -2107,28 +2107,28 @@
         <v>25.5</v>
       </c>
       <c r="M10">
-        <v>1.4413968</v>
+        <v>1.6215714</v>
       </c>
       <c r="N10">
-        <v>24.0586032</v>
+        <v>23.8784286</v>
       </c>
       <c r="O10">
-        <v>7.698753024</v>
+        <v>7.641097152</v>
       </c>
       <c r="P10">
-        <v>16.359850176</v>
+        <v>16.237331448</v>
       </c>
       <c r="Q10">
-        <v>24.859850176</v>
+        <v>24.737331448</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1214876149148326</v>
+        <v>0.1220680518829989</v>
       </c>
       <c r="T10">
-        <v>0.7319570829380426</v>
+        <v>0.7375703520379663</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.69117289562458</v>
+        <v>15.72548701833296</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.114160287213529</v>
+        <v>0.1138156487054119</v>
       </c>
       <c r="C11">
-        <v>342.5539356433698</v>
+        <v>340.8525293807582</v>
       </c>
       <c r="D11">
-        <v>371.1419356433698</v>
+        <v>373.0225293807582</v>
       </c>
       <c r="E11">
-        <v>-4.362000000000002</v>
+        <v>-0.7800000000000011</v>
       </c>
       <c r="F11">
-        <v>32.238</v>
+        <v>35.82</v>
       </c>
       <c r="G11">
         <v>3.65</v>
@@ -2189,28 +2189,28 @@
         <v>25.5</v>
       </c>
       <c r="M11">
-        <v>1.6215714</v>
+        <v>1.801746</v>
       </c>
       <c r="N11">
-        <v>23.8784286</v>
+        <v>23.698254</v>
       </c>
       <c r="O11">
-        <v>7.641097152</v>
+        <v>7.58344128</v>
       </c>
       <c r="P11">
-        <v>16.237331448</v>
+        <v>16.11481272</v>
       </c>
       <c r="Q11">
-        <v>24.737331448</v>
+        <v>24.61481272</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1220680518829989</v>
+        <v>0.1226613874504577</v>
       </c>
       <c r="T11">
-        <v>0.7375703520379663</v>
+        <v>0.7433083604512215</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.72548701833296</v>
+        <v>14.15293831649966</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1138156487054119</v>
+        <v>0.1135832101972948</v>
       </c>
       <c r="C12">
-        <v>340.8525293807582</v>
+        <v>338.5496780072536</v>
       </c>
       <c r="D12">
-        <v>373.0225293807582</v>
+        <v>374.3016780072537</v>
       </c>
       <c r="E12">
-        <v>-0.779999999999994</v>
+        <v>2.802000000000007</v>
       </c>
       <c r="F12">
-        <v>35.82000000000001</v>
+        <v>39.40200000000001</v>
       </c>
       <c r="G12">
         <v>3.65</v>
@@ -2271,45 +2271,45 @@
         <v>25.5</v>
       </c>
       <c r="M12">
-        <v>1.801746</v>
+        <v>2.0410236</v>
       </c>
       <c r="N12">
-        <v>23.698254</v>
+        <v>23.4589764</v>
       </c>
       <c r="O12">
-        <v>7.58344128</v>
+        <v>7.506872448</v>
       </c>
       <c r="P12">
-        <v>16.11481272</v>
+        <v>15.952103952</v>
       </c>
       <c r="Q12">
-        <v>24.61481272</v>
+        <v>24.452103952</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1226613874504577</v>
+        <v>0.1232680564014549</v>
       </c>
       <c r="T12">
-        <v>0.7433083604512215</v>
+        <v>0.7491753128737634</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.32</v>
       </c>
       <c r="W12">
-        <v>0.034204</v>
+        <v>0.035224</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>14.15293831649966</v>
+        <v>12.49373108669591</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1135832101972948</v>
+        <v>0.1132487716891778</v>
       </c>
       <c r="C13">
-        <v>338.5496780072536</v>
+        <v>336.8236183252675</v>
       </c>
       <c r="D13">
-        <v>374.3016780072537</v>
+        <v>376.1576183252675</v>
       </c>
       <c r="E13">
-        <v>2.802000000000007</v>
+        <v>6.384</v>
       </c>
       <c r="F13">
-        <v>39.40200000000001</v>
+        <v>42.984</v>
       </c>
       <c r="G13">
         <v>3.65</v>
@@ -2353,28 +2353,28 @@
         <v>25.5</v>
       </c>
       <c r="M13">
-        <v>2.0410236</v>
+        <v>2.2265712</v>
       </c>
       <c r="N13">
-        <v>23.4589764</v>
+        <v>23.2734288</v>
       </c>
       <c r="O13">
-        <v>7.506872448</v>
+        <v>7.447497216</v>
       </c>
       <c r="P13">
-        <v>15.952103952</v>
+        <v>15.825931584</v>
       </c>
       <c r="Q13">
-        <v>24.452103952</v>
+        <v>24.325931584</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1232680564014549</v>
+        <v>0.1238885132831566</v>
       </c>
       <c r="T13">
-        <v>0.7491753128737634</v>
+        <v>0.7551756051240904</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.49373108669591</v>
+        <v>11.45258682947125</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1132487716891778</v>
+        <v>0.1129143331810607</v>
       </c>
       <c r="C14">
-        <v>336.8236183252675</v>
+        <v>335.1160553751027</v>
       </c>
       <c r="D14">
-        <v>376.1576183252675</v>
+        <v>378.0320553751027</v>
       </c>
       <c r="E14">
-        <v>6.384</v>
+        <v>9.966000000000008</v>
       </c>
       <c r="F14">
-        <v>42.984</v>
+        <v>46.56600000000001</v>
       </c>
       <c r="G14">
         <v>3.65</v>
@@ -2435,28 +2435,28 @@
         <v>25.5</v>
       </c>
       <c r="M14">
-        <v>2.2265712</v>
+        <v>2.4121188</v>
       </c>
       <c r="N14">
-        <v>23.2734288</v>
+        <v>23.0878812</v>
       </c>
       <c r="O14">
-        <v>7.447497216</v>
+        <v>7.388121984</v>
       </c>
       <c r="P14">
-        <v>15.825931584</v>
+        <v>15.699759216</v>
       </c>
       <c r="Q14">
-        <v>24.325931584</v>
+        <v>24.199759216</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1238885132831566</v>
+        <v>0.1245232335414491</v>
       </c>
       <c r="T14">
-        <v>0.7551756051240904</v>
+        <v>0.7613138351272984</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.45258682947125</v>
+        <v>10.57161861181961</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1129143331810607</v>
+        <v>0.1125798946729436</v>
       </c>
       <c r="C15">
-        <v>335.1160553751027</v>
+        <v>333.4272670556433</v>
       </c>
       <c r="D15">
-        <v>378.0320553751027</v>
+        <v>379.9252670556434</v>
       </c>
       <c r="E15">
-        <v>9.966000000000008</v>
+        <v>13.54800000000001</v>
       </c>
       <c r="F15">
-        <v>46.56600000000001</v>
+        <v>50.14800000000001</v>
       </c>
       <c r="G15">
         <v>3.65</v>
@@ -2517,28 +2517,28 @@
         <v>25.5</v>
       </c>
       <c r="M15">
-        <v>2.4121188</v>
+        <v>2.5976664</v>
       </c>
       <c r="N15">
-        <v>23.0878812</v>
+        <v>22.9023336</v>
       </c>
       <c r="O15">
-        <v>7.388121984</v>
+        <v>7.328746752</v>
       </c>
       <c r="P15">
-        <v>15.699759216</v>
+        <v>15.573586848</v>
       </c>
       <c r="Q15">
-        <v>24.199759216</v>
+        <v>24.073586848</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1245232335414491</v>
+        <v>0.125172714735981</v>
       </c>
       <c r="T15">
-        <v>0.7613138351272984</v>
+        <v>0.7675948146654648</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.57161861181961</v>
+        <v>9.816502996689643</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1125798946729436</v>
+        <v>0.1124188561648266</v>
       </c>
       <c r="C16">
-        <v>333.4272670556433</v>
+        <v>330.763664664441</v>
       </c>
       <c r="D16">
-        <v>379.9252670556434</v>
+        <v>380.843664664441</v>
       </c>
       <c r="E16">
-        <v>13.54800000000001</v>
+        <v>17.13000000000002</v>
       </c>
       <c r="F16">
-        <v>50.14800000000001</v>
+        <v>53.73000000000002</v>
       </c>
       <c r="G16">
         <v>3.65</v>
@@ -2599,45 +2599,45 @@
         <v>25.5</v>
       </c>
       <c r="M16">
-        <v>2.5976664</v>
+        <v>2.874555000000001</v>
       </c>
       <c r="N16">
-        <v>22.9023336</v>
+        <v>22.625445</v>
       </c>
       <c r="O16">
-        <v>7.328746752</v>
+        <v>7.2401424</v>
       </c>
       <c r="P16">
-        <v>15.573586848</v>
+        <v>15.3853026</v>
       </c>
       <c r="Q16">
-        <v>24.073586848</v>
+        <v>23.8853026</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.125172714735981</v>
+        <v>0.1258374778409724</v>
       </c>
       <c r="T16">
-        <v>0.7675948146654648</v>
+        <v>0.7740235819574705</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.32</v>
       </c>
       <c r="W16">
-        <v>0.035224</v>
+        <v>0.03638</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>9.816502996689643</v>
+        <v>8.870938284360534</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1124188561648266</v>
+        <v>0.1120959776567095</v>
       </c>
       <c r="C17">
-        <v>330.763664664441</v>
+        <v>329.0364715263207</v>
       </c>
       <c r="D17">
-        <v>380.843664664441</v>
+        <v>382.6984715263208</v>
       </c>
       <c r="E17">
-        <v>17.13</v>
+        <v>20.71200000000001</v>
       </c>
       <c r="F17">
-        <v>53.73</v>
+        <v>57.31200000000001</v>
       </c>
       <c r="G17">
         <v>3.65</v>
@@ -2681,28 +2681,28 @@
         <v>25.5</v>
       </c>
       <c r="M17">
-        <v>2.874555</v>
+        <v>3.066192</v>
       </c>
       <c r="N17">
-        <v>22.625445</v>
+        <v>22.433808</v>
       </c>
       <c r="O17">
-        <v>7.2401424</v>
+        <v>7.17881856</v>
       </c>
       <c r="P17">
-        <v>15.3853026</v>
+        <v>15.25498944</v>
       </c>
       <c r="Q17">
-        <v>23.8853026</v>
+        <v>23.75498944</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1258374778409724</v>
+        <v>0.1265180686389399</v>
       </c>
       <c r="T17">
-        <v>0.7740235819574705</v>
+        <v>0.7806054151373809</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.870938284360536</v>
+        <v>8.316504641588001</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1120959776567095</v>
+        <v>0.1117730991485924</v>
       </c>
       <c r="C18">
-        <v>329.0364715263207</v>
+        <v>327.327433584186</v>
       </c>
       <c r="D18">
-        <v>382.6984715263208</v>
+        <v>384.571433584186</v>
       </c>
       <c r="E18">
-        <v>20.71200000000001</v>
+        <v>24.29400000000001</v>
       </c>
       <c r="F18">
-        <v>57.31200000000001</v>
+        <v>60.89400000000001</v>
       </c>
       <c r="G18">
         <v>3.65</v>
@@ -2763,28 +2763,28 @@
         <v>25.5</v>
       </c>
       <c r="M18">
-        <v>3.066192</v>
+        <v>3.257829000000001</v>
       </c>
       <c r="N18">
-        <v>22.433808</v>
+        <v>22.242171</v>
       </c>
       <c r="O18">
-        <v>7.17881856</v>
+        <v>7.11749472</v>
       </c>
       <c r="P18">
-        <v>15.25498944</v>
+        <v>15.12467628</v>
       </c>
       <c r="Q18">
-        <v>23.75498944</v>
+        <v>23.62467628</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1265180686389399</v>
+        <v>0.1272150592151716</v>
       </c>
       <c r="T18">
-        <v>0.7806054151373809</v>
+        <v>0.7873458467071687</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.316504641588001</v>
+        <v>7.827298486200472</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1117730991485924</v>
+        <v>0.1115481406404754</v>
       </c>
       <c r="C19">
-        <v>327.327433584186</v>
+        <v>325.0612520259061</v>
       </c>
       <c r="D19">
-        <v>384.571433584186</v>
+        <v>385.8872520259061</v>
       </c>
       <c r="E19">
-        <v>24.29400000000001</v>
+        <v>27.87600000000001</v>
       </c>
       <c r="F19">
-        <v>60.89400000000001</v>
+        <v>64.47600000000001</v>
       </c>
       <c r="G19">
         <v>3.65</v>
@@ -2845,45 +2845,45 @@
         <v>25.5</v>
       </c>
       <c r="M19">
-        <v>3.257829000000001</v>
+        <v>3.501046800000001</v>
       </c>
       <c r="N19">
-        <v>22.242171</v>
+        <v>21.9989532</v>
       </c>
       <c r="O19">
-        <v>7.11749472</v>
+        <v>7.039665024</v>
       </c>
       <c r="P19">
-        <v>15.12467628</v>
+        <v>14.959288176</v>
       </c>
       <c r="Q19">
-        <v>23.62467628</v>
+        <v>23.459288176</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1272150592151716</v>
+        <v>0.1279290495615553</v>
       </c>
       <c r="T19">
-        <v>0.7873458467071687</v>
+        <v>0.7942506790469512</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.32</v>
       </c>
       <c r="W19">
-        <v>0.03638</v>
+        <v>0.036924</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.827298486200472</v>
+        <v>7.283535884181839</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1115481406404754</v>
+        <v>0.1112307021323583</v>
       </c>
       <c r="C20">
-        <v>325.061252025906</v>
+        <v>323.3513926203429</v>
       </c>
       <c r="D20">
-        <v>385.887252025906</v>
+        <v>387.7593926203429</v>
       </c>
       <c r="E20">
-        <v>27.876</v>
+        <v>31.45800000000001</v>
       </c>
       <c r="F20">
-        <v>64.476</v>
+        <v>68.05800000000001</v>
       </c>
       <c r="G20">
         <v>3.65</v>
@@ -2927,28 +2927,28 @@
         <v>25.5</v>
       </c>
       <c r="M20">
-        <v>3.5010468</v>
+        <v>3.6955494</v>
       </c>
       <c r="N20">
-        <v>21.9989532</v>
+        <v>21.8044506</v>
       </c>
       <c r="O20">
-        <v>7.039665024</v>
+        <v>6.977424192</v>
       </c>
       <c r="P20">
-        <v>14.959288176</v>
+        <v>14.827026408</v>
       </c>
       <c r="Q20">
-        <v>23.459288176</v>
+        <v>23.327026408</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1279290495615553</v>
+        <v>0.1286606692992078</v>
       </c>
       <c r="T20">
-        <v>0.7942506790469512</v>
+        <v>0.801326001074136</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.283535884181839</v>
+        <v>6.900191890277531</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1112307021323583</v>
+        <v>0.1109132636242412</v>
       </c>
       <c r="C21">
-        <v>323.3513926203429</v>
+        <v>321.6597872381295</v>
       </c>
       <c r="D21">
-        <v>387.7593926203429</v>
+        <v>389.6497872381295</v>
       </c>
       <c r="E21">
-        <v>31.45800000000001</v>
+        <v>35.04000000000001</v>
       </c>
       <c r="F21">
-        <v>68.05800000000001</v>
+        <v>71.64000000000001</v>
       </c>
       <c r="G21">
         <v>3.65</v>
@@ -3009,28 +3009,28 @@
         <v>25.5</v>
       </c>
       <c r="M21">
-        <v>3.6955494</v>
+        <v>3.890052000000001</v>
       </c>
       <c r="N21">
-        <v>21.8044506</v>
+        <v>21.609948</v>
       </c>
       <c r="O21">
-        <v>6.977424192</v>
+        <v>6.91518336</v>
       </c>
       <c r="P21">
-        <v>14.827026408</v>
+        <v>14.69476464</v>
       </c>
       <c r="Q21">
-        <v>23.327026408</v>
+        <v>23.19476464</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1286606692992078</v>
+        <v>0.1294105795303016</v>
       </c>
       <c r="T21">
-        <v>0.801326001074136</v>
+        <v>0.8085782061520003</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.900191890277531</v>
+        <v>6.555182295763655</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1109132636242412</v>
+        <v>0.1105958251161242</v>
       </c>
       <c r="C22">
-        <v>321.6597872381295</v>
+        <v>319.9867041618253</v>
       </c>
       <c r="D22">
-        <v>389.6497872381295</v>
+        <v>391.5587041618253</v>
       </c>
       <c r="E22">
-        <v>35.04000000000001</v>
+        <v>38.62200000000002</v>
       </c>
       <c r="F22">
-        <v>71.64000000000001</v>
+        <v>75.22200000000002</v>
       </c>
       <c r="G22">
         <v>3.65</v>
@@ -3091,28 +3091,28 @@
         <v>25.5</v>
       </c>
       <c r="M22">
-        <v>3.890052000000001</v>
+        <v>4.084554600000001</v>
       </c>
       <c r="N22">
-        <v>21.609948</v>
+        <v>21.4154454</v>
       </c>
       <c r="O22">
-        <v>6.91518336</v>
+        <v>6.852942528</v>
       </c>
       <c r="P22">
-        <v>14.69476464</v>
+        <v>14.562502872</v>
       </c>
       <c r="Q22">
-        <v>23.19476464</v>
+        <v>23.062502872</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1294105795303016</v>
+        <v>0.1301794748305369</v>
       </c>
       <c r="T22">
-        <v>0.8085782061520003</v>
+        <v>0.8160140113584181</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.555182295763655</v>
+        <v>6.243030757870146</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1105958251161242</v>
+        <v>0.1104279866080071</v>
       </c>
       <c r="C23">
-        <v>319.9867041618253</v>
+        <v>317.4215798560254</v>
       </c>
       <c r="D23">
-        <v>391.5587041618253</v>
+        <v>392.5755798560255</v>
       </c>
       <c r="E23">
-        <v>38.62200000000001</v>
+        <v>42.20400000000001</v>
       </c>
       <c r="F23">
-        <v>75.22200000000001</v>
+        <v>78.80400000000002</v>
       </c>
       <c r="G23">
         <v>3.65</v>
@@ -3173,45 +3173,45 @@
         <v>25.5</v>
       </c>
       <c r="M23">
-        <v>4.084554600000001</v>
+        <v>4.357861200000001</v>
       </c>
       <c r="N23">
-        <v>21.4154454</v>
+        <v>21.1421388</v>
       </c>
       <c r="O23">
-        <v>6.852942528</v>
+        <v>6.765484416</v>
       </c>
       <c r="P23">
-        <v>14.562502872</v>
+        <v>14.376654384</v>
       </c>
       <c r="Q23">
-        <v>23.062502872</v>
+        <v>22.876654384</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1301794748305369</v>
+        <v>0.1309680853948809</v>
       </c>
       <c r="T23">
-        <v>0.8160140113584181</v>
+        <v>0.8236404782367954</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.32</v>
       </c>
       <c r="W23">
-        <v>0.036924</v>
+        <v>0.037604</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.243030757870147</v>
+        <v>5.851494306427197</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1104279866080071</v>
+        <v>0.1101173480998901</v>
       </c>
       <c r="C24">
-        <v>317.4215798560254</v>
+        <v>315.7356327259333</v>
       </c>
       <c r="D24">
-        <v>392.5755798560255</v>
+        <v>394.4716327259334</v>
       </c>
       <c r="E24">
-        <v>42.20400000000001</v>
+        <v>45.78600000000001</v>
       </c>
       <c r="F24">
-        <v>78.80400000000002</v>
+        <v>82.38600000000001</v>
       </c>
       <c r="G24">
         <v>3.65</v>
@@ -3255,28 +3255,28 @@
         <v>25.5</v>
       </c>
       <c r="M24">
-        <v>4.357861200000001</v>
+        <v>4.555945800000001</v>
       </c>
       <c r="N24">
-        <v>21.1421388</v>
+        <v>20.9440542</v>
       </c>
       <c r="O24">
-        <v>6.765484416</v>
+        <v>6.702097344</v>
       </c>
       <c r="P24">
-        <v>14.376654384</v>
+        <v>14.241956856</v>
       </c>
       <c r="Q24">
-        <v>22.876654384</v>
+        <v>22.741956856</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1309680853948809</v>
+        <v>0.1317771793505066</v>
       </c>
       <c r="T24">
-        <v>0.8236404782367954</v>
+        <v>0.8314650351639616</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.851494306427197</v>
+        <v>5.59708151049558</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1101173480998901</v>
+        <v>0.109806709591773</v>
       </c>
       <c r="C25">
-        <v>315.7356327259333</v>
+        <v>314.0680895112613</v>
       </c>
       <c r="D25">
-        <v>394.4716327259334</v>
+        <v>396.3860895112613</v>
       </c>
       <c r="E25">
-        <v>45.78600000000001</v>
+        <v>49.36800000000002</v>
       </c>
       <c r="F25">
-        <v>82.38600000000001</v>
+        <v>85.96800000000002</v>
       </c>
       <c r="G25">
         <v>3.65</v>
@@ -3337,28 +3337,28 @@
         <v>25.5</v>
       </c>
       <c r="M25">
-        <v>4.555945800000001</v>
+        <v>4.754030400000001</v>
       </c>
       <c r="N25">
-        <v>20.9440542</v>
+        <v>20.7459696</v>
       </c>
       <c r="O25">
-        <v>6.702097344</v>
+        <v>6.638710272</v>
       </c>
       <c r="P25">
-        <v>14.241956856</v>
+        <v>14.107259328</v>
       </c>
       <c r="Q25">
-        <v>22.741956856</v>
+        <v>22.607259328</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1317771793505066</v>
+        <v>0.1326075652523329</v>
       </c>
       <c r="T25">
-        <v>0.8314650351639616</v>
+        <v>0.839495501483948</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.59708151049558</v>
+        <v>5.363869780891597</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.109806709591773</v>
+        <v>0.1094960710836559</v>
       </c>
       <c r="C26">
-        <v>314.0680895112613</v>
+        <v>312.4192194734284</v>
       </c>
       <c r="D26">
-        <v>396.3860895112613</v>
+        <v>398.3192194734285</v>
       </c>
       <c r="E26">
-        <v>49.368</v>
+        <v>52.95000000000001</v>
       </c>
       <c r="F26">
-        <v>85.968</v>
+        <v>89.55000000000001</v>
       </c>
       <c r="G26">
         <v>3.65</v>
@@ -3419,28 +3419,28 @@
         <v>25.5</v>
       </c>
       <c r="M26">
-        <v>4.7540304</v>
+        <v>4.952115000000001</v>
       </c>
       <c r="N26">
-        <v>20.7459696</v>
+        <v>20.547885</v>
       </c>
       <c r="O26">
-        <v>6.638710272</v>
+        <v>6.575323200000001</v>
       </c>
       <c r="P26">
-        <v>14.107259328</v>
+        <v>13.9725618</v>
       </c>
       <c r="Q26">
-        <v>22.607259328</v>
+        <v>22.4725618</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1326075652523329</v>
+        <v>0.1334600947782079</v>
       </c>
       <c r="T26">
-        <v>0.839495501483948</v>
+        <v>0.8477401135724675</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.363869780891598</v>
+        <v>5.149314989655934</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1094960710836559</v>
+        <v>0.1091854325755389</v>
       </c>
       <c r="C27">
-        <v>312.4192194734284</v>
+        <v>310.789297152225</v>
       </c>
       <c r="D27">
-        <v>398.3192194734285</v>
+        <v>400.271297152225</v>
       </c>
       <c r="E27">
-        <v>52.95000000000001</v>
+        <v>56.53200000000002</v>
       </c>
       <c r="F27">
-        <v>89.55000000000001</v>
+        <v>93.13200000000002</v>
       </c>
       <c r="G27">
         <v>3.65</v>
@@ -3501,28 +3501,28 @@
         <v>25.5</v>
       </c>
       <c r="M27">
-        <v>4.952115000000001</v>
+        <v>5.150199600000001</v>
       </c>
       <c r="N27">
-        <v>20.547885</v>
+        <v>20.3498004</v>
       </c>
       <c r="O27">
-        <v>6.575323200000001</v>
+        <v>6.511936128</v>
       </c>
       <c r="P27">
-        <v>13.9725618</v>
+        <v>13.837864272</v>
       </c>
       <c r="Q27">
-        <v>22.4725618</v>
+        <v>22.337864272</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1334600947782079</v>
+        <v>0.1343356656426201</v>
       </c>
       <c r="T27">
-        <v>0.8477401135724675</v>
+        <v>0.8562075530147307</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.149314989655934</v>
+        <v>4.951264413130705</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1091854325755389</v>
+        <v>0.1088747940674218</v>
       </c>
       <c r="C28">
-        <v>310.789297152225</v>
+        <v>309.1786024957912</v>
       </c>
       <c r="D28">
-        <v>400.271297152225</v>
+        <v>402.2426024957912</v>
       </c>
       <c r="E28">
-        <v>56.53200000000002</v>
+        <v>60.11400000000001</v>
       </c>
       <c r="F28">
-        <v>93.13200000000002</v>
+        <v>96.71400000000001</v>
       </c>
       <c r="G28">
         <v>3.65</v>
@@ -3583,28 +3583,28 @@
         <v>25.5</v>
       </c>
       <c r="M28">
-        <v>5.150199600000001</v>
+        <v>5.348284200000001</v>
       </c>
       <c r="N28">
-        <v>20.3498004</v>
+        <v>20.1517158</v>
       </c>
       <c r="O28">
-        <v>6.511936128</v>
+        <v>6.448549055999999</v>
       </c>
       <c r="P28">
-        <v>13.837864272</v>
+        <v>13.703166744</v>
       </c>
       <c r="Q28">
-        <v>22.337864272</v>
+        <v>22.203166744</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1343356656426201</v>
+        <v>0.1352352247498929</v>
       </c>
       <c r="T28">
-        <v>0.8562075530147307</v>
+        <v>0.8649069770992477</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.951264413130705</v>
+        <v>4.76788424968142</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1088747940674218</v>
+        <v>0.1085641555593047</v>
       </c>
       <c r="C29">
-        <v>309.1786024957912</v>
+        <v>307.5874209944541</v>
       </c>
       <c r="D29">
-        <v>402.2426024957912</v>
+        <v>404.2334209944541</v>
       </c>
       <c r="E29">
-        <v>60.11400000000001</v>
+        <v>63.69600000000002</v>
       </c>
       <c r="F29">
-        <v>96.71400000000001</v>
+        <v>100.296</v>
       </c>
       <c r="G29">
         <v>3.65</v>
@@ -3665,28 +3665,28 @@
         <v>25.5</v>
       </c>
       <c r="M29">
-        <v>5.348284200000001</v>
+        <v>5.546368800000002</v>
       </c>
       <c r="N29">
-        <v>20.1517158</v>
+        <v>19.9536312</v>
       </c>
       <c r="O29">
-        <v>6.448549055999999</v>
+        <v>6.385161983999999</v>
       </c>
       <c r="P29">
-        <v>13.703166744</v>
+        <v>13.568469216</v>
       </c>
       <c r="Q29">
-        <v>22.203166744</v>
+        <v>22.068469216</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1352352247498929</v>
+        <v>0.1361597716101455</v>
       </c>
       <c r="T29">
-        <v>0.8649069770992477</v>
+        <v>0.873848051852779</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.76788424968142</v>
+        <v>4.597602669335655</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1085641555593047</v>
+        <v>0.1087465170511877</v>
       </c>
       <c r="C30">
-        <v>307.5874209944541</v>
+        <v>302.8343218904076</v>
       </c>
       <c r="D30">
-        <v>404.2334209944541</v>
+        <v>403.0623218904076</v>
       </c>
       <c r="E30">
-        <v>63.69600000000002</v>
+        <v>67.27800000000002</v>
       </c>
       <c r="F30">
-        <v>100.296</v>
+        <v>103.878</v>
       </c>
       <c r="G30">
         <v>3.65</v>
@@ -3747,45 +3747,45 @@
         <v>25.5</v>
       </c>
       <c r="M30">
-        <v>5.546368800000002</v>
+        <v>6.004148400000002</v>
       </c>
       <c r="N30">
-        <v>19.9536312</v>
+        <v>19.4958516</v>
       </c>
       <c r="O30">
-        <v>6.385161983999999</v>
+        <v>6.238672512</v>
       </c>
       <c r="P30">
-        <v>13.568469216</v>
+        <v>13.257179088</v>
       </c>
       <c r="Q30">
-        <v>22.068469216</v>
+        <v>21.757179088</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1361597716101455</v>
+        <v>0.1371103620439263</v>
       </c>
       <c r="T30">
-        <v>0.873848051852779</v>
+        <v>0.8830409878669732</v>
       </c>
       <c r="U30">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V30">
         <v>0.32</v>
       </c>
       <c r="W30">
-        <v>0.037604</v>
+        <v>0.039304</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.597602669335655</v>
+        <v>4.247063580240621</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1087465170511877</v>
+        <v>0.1084528785430706</v>
       </c>
       <c r="C31">
-        <v>302.8343218904076</v>
+        <v>301.1413750613124</v>
       </c>
       <c r="D31">
-        <v>403.0623218904076</v>
+        <v>404.9513750613124</v>
       </c>
       <c r="E31">
-        <v>67.27799999999999</v>
+        <v>70.86000000000001</v>
       </c>
       <c r="F31">
-        <v>103.878</v>
+        <v>107.46</v>
       </c>
       <c r="G31">
         <v>3.65</v>
@@ -3829,28 +3829,28 @@
         <v>25.5</v>
       </c>
       <c r="M31">
-        <v>6.0041484</v>
+        <v>6.211188000000001</v>
       </c>
       <c r="N31">
-        <v>19.4958516</v>
+        <v>19.288812</v>
       </c>
       <c r="O31">
-        <v>6.238672512000001</v>
+        <v>6.17241984</v>
       </c>
       <c r="P31">
-        <v>13.257179088</v>
+        <v>13.11639216</v>
       </c>
       <c r="Q31">
-        <v>21.757179088</v>
+        <v>21.61639216</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1371103620439263</v>
+        <v>0.1380881122043866</v>
       </c>
       <c r="T31">
-        <v>0.8830409878669732</v>
+        <v>0.8924965791958586</v>
       </c>
       <c r="U31">
         <v>0.0578</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.247063580240622</v>
+        <v>4.1054947942326</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1084528785430706</v>
+        <v>0.1088970400349535</v>
       </c>
       <c r="C32">
-        <v>301.1413750613124</v>
+        <v>294.7087848151195</v>
       </c>
       <c r="D32">
-        <v>404.9513750613124</v>
+        <v>402.1007848151196</v>
       </c>
       <c r="E32">
-        <v>70.86000000000001</v>
+        <v>74.44200000000001</v>
       </c>
       <c r="F32">
-        <v>107.46</v>
+        <v>111.042</v>
       </c>
       <c r="G32">
         <v>3.65</v>
@@ -3911,45 +3911,45 @@
         <v>25.5</v>
       </c>
       <c r="M32">
-        <v>6.211188000000001</v>
+        <v>6.806874600000001</v>
       </c>
       <c r="N32">
-        <v>19.288812</v>
+        <v>18.6931254</v>
       </c>
       <c r="O32">
-        <v>6.17241984</v>
+        <v>5.981800128</v>
       </c>
       <c r="P32">
-        <v>13.11639216</v>
+        <v>12.711325272</v>
       </c>
       <c r="Q32">
-        <v>21.61639216</v>
+        <v>21.211325272</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1380881122043866</v>
+        <v>0.139094202949208</v>
       </c>
       <c r="T32">
-        <v>0.8924965791958586</v>
+        <v>0.9022262456357263</v>
       </c>
       <c r="U32">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V32">
         <v>0.32</v>
       </c>
       <c r="W32">
-        <v>0.039304</v>
+        <v>0.041684</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.1054947942326</v>
+        <v>3.746212689153991</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1088970400349535</v>
+        <v>0.1086272015268365</v>
       </c>
       <c r="C33">
-        <v>294.7087848151195</v>
+        <v>292.8537800218195</v>
       </c>
       <c r="D33">
-        <v>402.1007848151196</v>
+        <v>403.8277800218196</v>
       </c>
       <c r="E33">
-        <v>74.44200000000001</v>
+        <v>78.02400000000003</v>
       </c>
       <c r="F33">
-        <v>111.042</v>
+        <v>114.624</v>
       </c>
       <c r="G33">
         <v>3.65</v>
@@ -3993,28 +3993,28 @@
         <v>25.5</v>
       </c>
       <c r="M33">
-        <v>6.806874600000001</v>
+        <v>7.026451200000001</v>
       </c>
       <c r="N33">
-        <v>18.6931254</v>
+        <v>18.4735488</v>
       </c>
       <c r="O33">
-        <v>5.981800128</v>
+        <v>5.911535616</v>
       </c>
       <c r="P33">
-        <v>12.711325272</v>
+        <v>12.562013184</v>
       </c>
       <c r="Q33">
-        <v>21.211325272</v>
+        <v>21.062013184</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.139094202949208</v>
+        <v>0.1401298845982889</v>
       </c>
       <c r="T33">
-        <v>0.9022262456357263</v>
+        <v>0.91224207873559</v>
       </c>
       <c r="U33">
         <v>0.0613</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.746212689153991</v>
+        <v>3.629143542617929</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1086272015268365</v>
+        <v>0.1083573630187194</v>
       </c>
       <c r="C34">
-        <v>292.8537800218195</v>
+        <v>291.0136738683473</v>
       </c>
       <c r="D34">
-        <v>403.8277800218196</v>
+        <v>405.5696738683474</v>
       </c>
       <c r="E34">
-        <v>78.02400000000003</v>
+        <v>81.60600000000002</v>
       </c>
       <c r="F34">
-        <v>114.624</v>
+        <v>118.206</v>
       </c>
       <c r="G34">
         <v>3.65</v>
@@ -4075,28 +4075,28 @@
         <v>25.5</v>
       </c>
       <c r="M34">
-        <v>7.026451200000001</v>
+        <v>7.246027800000001</v>
       </c>
       <c r="N34">
-        <v>18.4735488</v>
+        <v>18.2539722</v>
       </c>
       <c r="O34">
-        <v>5.911535616</v>
+        <v>5.841271104</v>
       </c>
       <c r="P34">
-        <v>12.562013184</v>
+        <v>12.412701096</v>
       </c>
       <c r="Q34">
-        <v>21.062013184</v>
+        <v>20.912701096</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1401298845982889</v>
+        <v>0.1411964821174917</v>
       </c>
       <c r="T34">
-        <v>0.91224207873559</v>
+        <v>0.9225568919279871</v>
       </c>
       <c r="U34">
         <v>0.0613</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.629143542617929</v>
+        <v>3.519169495871931</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1083573630187194</v>
+        <v>0.1087348845106023</v>
       </c>
       <c r="C35">
-        <v>291.0136738683473</v>
+        <v>284.9988217302702</v>
       </c>
       <c r="D35">
-        <v>405.5696738683474</v>
+        <v>403.1368217302702</v>
       </c>
       <c r="E35">
-        <v>81.60600000000002</v>
+        <v>85.18800000000002</v>
       </c>
       <c r="F35">
-        <v>118.206</v>
+        <v>121.788</v>
       </c>
       <c r="G35">
         <v>3.65</v>
@@ -4157,45 +4157,45 @@
         <v>25.5</v>
       </c>
       <c r="M35">
-        <v>7.246027800000001</v>
+        <v>7.806610800000002</v>
       </c>
       <c r="N35">
-        <v>18.2539722</v>
+        <v>17.6933892</v>
       </c>
       <c r="O35">
-        <v>5.841271104</v>
+        <v>5.661884543999999</v>
       </c>
       <c r="P35">
-        <v>12.412701096</v>
+        <v>12.031504656</v>
       </c>
       <c r="Q35">
-        <v>20.912701096</v>
+        <v>20.531504656</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1411964821174917</v>
+        <v>0.1422954007736399</v>
       </c>
       <c r="T35">
-        <v>0.9225568919279871</v>
+        <v>0.9331842752171233</v>
       </c>
       <c r="U35">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V35">
         <v>0.32</v>
       </c>
       <c r="W35">
-        <v>0.041684</v>
+        <v>0.043588</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.519169495871931</v>
+        <v>3.266462316784128</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1087348845106023</v>
+        <v>0.1084840860024853</v>
       </c>
       <c r="C36">
-        <v>284.9988217302702</v>
+        <v>283.0297688099006</v>
       </c>
       <c r="D36">
-        <v>403.1368217302702</v>
+        <v>404.7497688099007</v>
       </c>
       <c r="E36">
-        <v>85.18800000000002</v>
+        <v>88.77000000000004</v>
       </c>
       <c r="F36">
-        <v>121.788</v>
+        <v>125.37</v>
       </c>
       <c r="G36">
         <v>3.65</v>
@@ -4239,28 +4239,28 @@
         <v>25.5</v>
       </c>
       <c r="M36">
-        <v>7.806610800000002</v>
+        <v>8.036217000000002</v>
       </c>
       <c r="N36">
-        <v>17.6933892</v>
+        <v>17.463783</v>
       </c>
       <c r="O36">
-        <v>5.661884543999999</v>
+        <v>5.58841056</v>
       </c>
       <c r="P36">
-        <v>12.031504656</v>
+        <v>11.87537244</v>
       </c>
       <c r="Q36">
-        <v>20.531504656</v>
+        <v>20.37537244</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1422954007736399</v>
+        <v>0.1434281323115158</v>
       </c>
       <c r="T36">
-        <v>0.9331842752171233</v>
+        <v>0.9441386549151563</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.266462316784128</v>
+        <v>3.173134822018867</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1084840860024853</v>
+        <v>0.1082332874943682</v>
       </c>
       <c r="C37">
-        <v>283.0297688099006</v>
+        <v>281.0736745126461</v>
       </c>
       <c r="D37">
-        <v>404.7497688099007</v>
+        <v>406.3756745126462</v>
       </c>
       <c r="E37">
-        <v>88.77000000000004</v>
+        <v>92.35200000000003</v>
       </c>
       <c r="F37">
-        <v>125.37</v>
+        <v>128.952</v>
       </c>
       <c r="G37">
         <v>3.65</v>
@@ -4321,28 +4321,28 @@
         <v>25.5</v>
       </c>
       <c r="M37">
-        <v>8.036217000000002</v>
+        <v>8.265823200000002</v>
       </c>
       <c r="N37">
-        <v>17.463783</v>
+        <v>17.2341768</v>
       </c>
       <c r="O37">
-        <v>5.58841056</v>
+        <v>5.514936576</v>
       </c>
       <c r="P37">
-        <v>11.87537244</v>
+        <v>11.719240224</v>
       </c>
       <c r="Q37">
-        <v>20.37537244</v>
+        <v>20.219240224</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1434281323115158</v>
+        <v>0.1445962617099504</v>
       </c>
       <c r="T37">
-        <v>0.9441386549151563</v>
+        <v>0.9554353589787525</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.173134822018867</v>
+        <v>3.084992188073899</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1082332874943682</v>
+        <v>0.1079824889862512</v>
       </c>
       <c r="C38">
-        <v>281.0736745126462</v>
+        <v>279.1306956352224</v>
       </c>
       <c r="D38">
-        <v>406.3756745126462</v>
+        <v>408.0146956352225</v>
       </c>
       <c r="E38">
-        <v>92.352</v>
+        <v>95.93400000000003</v>
       </c>
       <c r="F38">
-        <v>128.952</v>
+        <v>132.534</v>
       </c>
       <c r="G38">
         <v>3.65</v>
@@ -4403,28 +4403,28 @@
         <v>25.5</v>
       </c>
       <c r="M38">
-        <v>8.2658232</v>
+        <v>8.495429400000003</v>
       </c>
       <c r="N38">
-        <v>17.2341768</v>
+        <v>17.0045706</v>
       </c>
       <c r="O38">
-        <v>5.514936576</v>
+        <v>5.441462592</v>
       </c>
       <c r="P38">
-        <v>11.719240224</v>
+        <v>11.563108008</v>
       </c>
       <c r="Q38">
-        <v>20.219240224</v>
+        <v>20.063108008</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1445962617099503</v>
+        <v>0.145801474581351</v>
       </c>
       <c r="T38">
-        <v>0.9554353589787523</v>
+        <v>0.9670906885681773</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.084992188073899</v>
+        <v>3.001614020828658</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1079824889862512</v>
+        <v>0.1097472104781341</v>
       </c>
       <c r="C39">
-        <v>279.1306956352224</v>
+        <v>264.2889034252439</v>
       </c>
       <c r="D39">
-        <v>408.0146956352225</v>
+        <v>396.7549034252439</v>
       </c>
       <c r="E39">
-        <v>95.93400000000003</v>
+        <v>99.51600000000002</v>
       </c>
       <c r="F39">
-        <v>132.534</v>
+        <v>136.116</v>
       </c>
       <c r="G39">
         <v>3.65</v>
@@ -4485,45 +4485,45 @@
         <v>25.5</v>
       </c>
       <c r="M39">
-        <v>8.495429400000003</v>
+        <v>9.786740400000001</v>
       </c>
       <c r="N39">
-        <v>17.0045706</v>
+        <v>15.7132596</v>
       </c>
       <c r="O39">
-        <v>5.441462592</v>
+        <v>5.028243072</v>
       </c>
       <c r="P39">
-        <v>11.563108008</v>
+        <v>10.685016528</v>
       </c>
       <c r="Q39">
-        <v>20.063108008</v>
+        <v>19.185016528</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.145801474581351</v>
+        <v>0.1470455652873131</v>
       </c>
       <c r="T39">
-        <v>0.9670906885681773</v>
+        <v>0.9791219965314544</v>
       </c>
       <c r="U39">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V39">
         <v>0.32</v>
       </c>
       <c r="W39">
-        <v>0.043588</v>
+        <v>0.048892</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.001614020828658</v>
+        <v>2.605566200570723</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1097472104781341</v>
+        <v>0.109549451970017</v>
       </c>
       <c r="C40">
-        <v>264.2889034252439</v>
+        <v>261.9376851082992</v>
       </c>
       <c r="D40">
-        <v>396.7549034252439</v>
+        <v>397.9856851082993</v>
       </c>
       <c r="E40">
-        <v>99.51600000000002</v>
+        <v>103.098</v>
       </c>
       <c r="F40">
-        <v>136.116</v>
+        <v>139.698</v>
       </c>
       <c r="G40">
         <v>3.65</v>
@@ -4567,28 +4567,28 @@
         <v>25.5</v>
       </c>
       <c r="M40">
-        <v>9.786740400000001</v>
+        <v>10.0442862</v>
       </c>
       <c r="N40">
-        <v>15.7132596</v>
+        <v>15.4557138</v>
       </c>
       <c r="O40">
-        <v>5.028243072</v>
+        <v>4.945828415999999</v>
       </c>
       <c r="P40">
-        <v>10.685016528</v>
+        <v>10.509885384</v>
       </c>
       <c r="Q40">
-        <v>19.185016528</v>
+        <v>19.009885384</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1470455652873131</v>
+        <v>0.1483304458524869</v>
       </c>
       <c r="T40">
-        <v>0.9791219965314544</v>
+        <v>0.9915477736082816</v>
       </c>
       <c r="U40">
         <v>0.07190000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.605566200570723</v>
+        <v>2.538756810812499</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.109549451970017</v>
+        <v>0.1104124934619</v>
       </c>
       <c r="C41">
-        <v>261.9376851082992</v>
+        <v>253.039713830601</v>
       </c>
       <c r="D41">
-        <v>397.9856851082993</v>
+        <v>392.6697138306011</v>
       </c>
       <c r="E41">
-        <v>103.098</v>
+        <v>106.68</v>
       </c>
       <c r="F41">
-        <v>139.698</v>
+        <v>143.28</v>
       </c>
       <c r="G41">
         <v>3.65</v>
@@ -4649,45 +4649,45 @@
         <v>25.5</v>
       </c>
       <c r="M41">
-        <v>10.0442862</v>
+        <v>10.860624</v>
       </c>
       <c r="N41">
-        <v>15.4557138</v>
+        <v>14.639376</v>
       </c>
       <c r="O41">
-        <v>4.945828415999999</v>
+        <v>4.684600319999999</v>
       </c>
       <c r="P41">
-        <v>10.509885384</v>
+        <v>9.954775679999997</v>
       </c>
       <c r="Q41">
-        <v>19.009885384</v>
+        <v>18.45477568</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1483304458524869</v>
+        <v>0.1496581557698333</v>
       </c>
       <c r="T41">
-        <v>0.9915477736082816</v>
+        <v>1.004387743254336</v>
       </c>
       <c r="U41">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V41">
         <v>0.32</v>
       </c>
       <c r="W41">
-        <v>0.048892</v>
+        <v>0.051544</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.538756810812499</v>
+        <v>2.347931389577615</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1104124934619</v>
+        <v>0.1102412549537829</v>
       </c>
       <c r="C42">
-        <v>253.039713830601</v>
+        <v>250.5011475133766</v>
       </c>
       <c r="D42">
-        <v>392.6697138306011</v>
+        <v>393.7131475133766</v>
       </c>
       <c r="E42">
-        <v>106.68</v>
+        <v>110.262</v>
       </c>
       <c r="F42">
-        <v>143.28</v>
+        <v>146.862</v>
       </c>
       <c r="G42">
         <v>3.65</v>
@@ -4731,28 +4731,28 @@
         <v>25.5</v>
       </c>
       <c r="M42">
-        <v>10.860624</v>
+        <v>11.1321396</v>
       </c>
       <c r="N42">
-        <v>14.639376</v>
+        <v>14.3678604</v>
       </c>
       <c r="O42">
-        <v>4.684600319999999</v>
+        <v>4.597715328</v>
       </c>
       <c r="P42">
-        <v>9.954775679999997</v>
+        <v>9.770145071999998</v>
       </c>
       <c r="Q42">
-        <v>18.45477568</v>
+        <v>18.270145072</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1496581557698333</v>
+        <v>0.1510308728030219</v>
       </c>
       <c r="T42">
-        <v>1.004387743254336</v>
+        <v>1.017662966108732</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.347931389577615</v>
+        <v>2.290664770319625</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1102412549537829</v>
+        <v>0.1100700164456658</v>
       </c>
       <c r="C43">
-        <v>250.5011475133766</v>
+        <v>247.9681413636157</v>
       </c>
       <c r="D43">
-        <v>393.7131475133766</v>
+        <v>394.7621413636158</v>
       </c>
       <c r="E43">
-        <v>110.262</v>
+        <v>113.8440000000001</v>
       </c>
       <c r="F43">
-        <v>146.862</v>
+        <v>150.444</v>
       </c>
       <c r="G43">
         <v>3.65</v>
@@ -4813,28 +4813,28 @@
         <v>25.5</v>
       </c>
       <c r="M43">
-        <v>11.1321396</v>
+        <v>11.4036552</v>
       </c>
       <c r="N43">
-        <v>14.3678604</v>
+        <v>14.0963448</v>
       </c>
       <c r="O43">
-        <v>4.597715328</v>
+        <v>4.510830335999999</v>
       </c>
       <c r="P43">
-        <v>9.770145071999998</v>
+        <v>9.585514463999996</v>
       </c>
       <c r="Q43">
-        <v>18.270145072</v>
+        <v>18.085514464</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1510308728030219</v>
+        <v>0.1524509249063204</v>
       </c>
       <c r="T43">
-        <v>1.017662966108732</v>
+        <v>1.031395955268452</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.290664770319625</v>
+        <v>2.236125132931061</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1100700164456658</v>
+        <v>0.1098987779375488</v>
       </c>
       <c r="C44">
-        <v>247.9681413636156</v>
+        <v>245.4407399429217</v>
       </c>
       <c r="D44">
-        <v>394.7621413636156</v>
+        <v>395.8167399429217</v>
       </c>
       <c r="E44">
-        <v>113.844</v>
+        <v>117.426</v>
       </c>
       <c r="F44">
-        <v>150.444</v>
+        <v>154.026</v>
       </c>
       <c r="G44">
         <v>3.65</v>
@@ -4895,28 +4895,28 @@
         <v>25.5</v>
       </c>
       <c r="M44">
-        <v>11.4036552</v>
+        <v>11.6751708</v>
       </c>
       <c r="N44">
-        <v>14.0963448</v>
+        <v>13.8248292</v>
       </c>
       <c r="O44">
-        <v>4.510830335999999</v>
+        <v>4.423945344</v>
       </c>
       <c r="P44">
-        <v>9.585514463999999</v>
+        <v>9.400883855999998</v>
       </c>
       <c r="Q44">
-        <v>18.085514464</v>
+        <v>17.900883856</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1524509249063204</v>
+        <v>0.1539208033992084</v>
       </c>
       <c r="T44">
-        <v>1.031395955268452</v>
+        <v>1.045610803696934</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.236125132931062</v>
+        <v>2.184122222862898</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1098987779375488</v>
+        <v>0.1097275394294317</v>
       </c>
       <c r="C45">
-        <v>245.4407399429217</v>
+        <v>242.9189882903559</v>
       </c>
       <c r="D45">
-        <v>395.8167399429217</v>
+        <v>396.876988290356</v>
       </c>
       <c r="E45">
-        <v>117.426</v>
+        <v>121.008</v>
       </c>
       <c r="F45">
-        <v>154.026</v>
+        <v>157.608</v>
       </c>
       <c r="G45">
         <v>3.65</v>
@@ -4977,28 +4977,28 @@
         <v>25.5</v>
       </c>
       <c r="M45">
-        <v>11.6751708</v>
+        <v>11.9466864</v>
       </c>
       <c r="N45">
-        <v>13.8248292</v>
+        <v>13.5533136</v>
       </c>
       <c r="O45">
-        <v>4.423945344</v>
+        <v>4.337060351999999</v>
       </c>
       <c r="P45">
-        <v>9.400883855999998</v>
+        <v>9.216253247999997</v>
       </c>
       <c r="Q45">
-        <v>17.900883856</v>
+        <v>17.716253248</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1539208033992084</v>
+        <v>0.1554431775525566</v>
       </c>
       <c r="T45">
-        <v>1.045610803696934</v>
+        <v>1.060333325283575</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.184122222862898</v>
+        <v>2.134483081434195</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1097275394294317</v>
+        <v>0.1095563009213146</v>
       </c>
       <c r="C46">
-        <v>242.9189882903559</v>
+        <v>240.4029319288476</v>
       </c>
       <c r="D46">
-        <v>396.876988290356</v>
+        <v>397.9429319288477</v>
       </c>
       <c r="E46">
-        <v>121.008</v>
+        <v>124.59</v>
       </c>
       <c r="F46">
-        <v>157.608</v>
+        <v>161.19</v>
       </c>
       <c r="G46">
         <v>3.65</v>
@@ -5059,28 +5059,28 @@
         <v>25.5</v>
       </c>
       <c r="M46">
-        <v>11.9466864</v>
+        <v>12.218202</v>
       </c>
       <c r="N46">
-        <v>13.5533136</v>
+        <v>13.281798</v>
       </c>
       <c r="O46">
-        <v>4.337060351999999</v>
+        <v>4.250175359999999</v>
       </c>
       <c r="P46">
-        <v>9.216253247999997</v>
+        <v>9.031622639999998</v>
       </c>
       <c r="Q46">
-        <v>17.716253248</v>
+        <v>17.53162264</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1554431775525566</v>
+        <v>0.1570209107660266</v>
       </c>
       <c r="T46">
-        <v>1.060333325283575</v>
+        <v>1.07559121129155</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.134483081434195</v>
+        <v>2.087050124068991</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1095563009213146</v>
+        <v>0.1093850624131976</v>
       </c>
       <c r="C47">
-        <v>240.4029319288476</v>
+        <v>237.8926168717105</v>
       </c>
       <c r="D47">
-        <v>397.9429319288477</v>
+        <v>399.0146168717105</v>
       </c>
       <c r="E47">
-        <v>124.59</v>
+        <v>128.172</v>
       </c>
       <c r="F47">
-        <v>161.19</v>
+        <v>164.772</v>
       </c>
       <c r="G47">
         <v>3.65</v>
@@ -5141,28 +5141,28 @@
         <v>25.5</v>
       </c>
       <c r="M47">
-        <v>12.218202</v>
+        <v>12.4897176</v>
       </c>
       <c r="N47">
-        <v>13.281798</v>
+        <v>13.0102824</v>
       </c>
       <c r="O47">
-        <v>4.250175359999999</v>
+        <v>4.163290367999999</v>
       </c>
       <c r="P47">
-        <v>9.031622639999998</v>
+        <v>8.846992031999999</v>
       </c>
       <c r="Q47">
-        <v>17.53162264</v>
+        <v>17.346992032</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1570209107660266</v>
+        <v>0.1586570785429585</v>
       </c>
       <c r="T47">
-        <v>1.07559121129155</v>
+        <v>1.091414204188708</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.087050124068991</v>
+        <v>2.041679469197926</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1093850624131976</v>
+        <v>0.1137521439050805</v>
       </c>
       <c r="C48">
-        <v>237.8926168717105</v>
+        <v>208.6671382676318</v>
       </c>
       <c r="D48">
-        <v>399.0146168717105</v>
+        <v>373.3711382676319</v>
       </c>
       <c r="E48">
-        <v>128.172</v>
+        <v>131.754</v>
       </c>
       <c r="F48">
-        <v>164.772</v>
+        <v>168.354</v>
       </c>
       <c r="G48">
         <v>3.65</v>
@@ -5223,45 +5223,45 @@
         <v>25.5</v>
       </c>
       <c r="M48">
-        <v>12.4897176</v>
+        <v>15.15186</v>
       </c>
       <c r="N48">
-        <v>13.0102824</v>
+        <v>10.34814</v>
       </c>
       <c r="O48">
-        <v>4.163290367999999</v>
+        <v>3.311404799999999</v>
       </c>
       <c r="P48">
-        <v>8.846992031999999</v>
+        <v>7.036735199999998</v>
       </c>
       <c r="Q48">
-        <v>17.346992032</v>
+        <v>15.5367352</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1586570785429585</v>
+        <v>0.1603549885001519</v>
       </c>
       <c r="T48">
-        <v>1.091414204188708</v>
+        <v>1.107834291157457</v>
       </c>
       <c r="U48">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V48">
         <v>0.32</v>
       </c>
       <c r="W48">
-        <v>0.051544</v>
+        <v>0.06119999999999999</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.041679469197926</v>
+        <v>1.682961695791803</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1137521439050805</v>
+        <v>0.1136774653969635</v>
       </c>
       <c r="C49">
-        <v>208.6671382676318</v>
+        <v>205.4959196575487</v>
       </c>
       <c r="D49">
-        <v>373.3711382676319</v>
+        <v>373.7819196575487</v>
       </c>
       <c r="E49">
-        <v>131.754</v>
+        <v>135.336</v>
       </c>
       <c r="F49">
-        <v>168.354</v>
+        <v>171.936</v>
       </c>
       <c r="G49">
         <v>3.65</v>
@@ -5305,28 +5305,28 @@
         <v>25.5</v>
       </c>
       <c r="M49">
-        <v>15.15186</v>
+        <v>15.47424</v>
       </c>
       <c r="N49">
-        <v>10.34814</v>
+        <v>10.02576</v>
       </c>
       <c r="O49">
-        <v>3.311404799999999</v>
+        <v>3.2082432</v>
       </c>
       <c r="P49">
-        <v>7.036735199999998</v>
+        <v>6.817516799999998</v>
       </c>
       <c r="Q49">
-        <v>15.5367352</v>
+        <v>15.3175168</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1603549885001519</v>
+        <v>0.1621182026864682</v>
       </c>
       <c r="T49">
-        <v>1.107834291157457</v>
+        <v>1.124885919932697</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.682961695791803</v>
+        <v>1.647899993796141</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1136774653969635</v>
+        <v>0.1136027868888464</v>
       </c>
       <c r="C50">
-        <v>205.4959196575487</v>
+        <v>202.3256059229957</v>
       </c>
       <c r="D50">
-        <v>373.7819196575487</v>
+        <v>374.1936059229957</v>
       </c>
       <c r="E50">
-        <v>135.336</v>
+        <v>138.918</v>
       </c>
       <c r="F50">
-        <v>171.936</v>
+        <v>175.518</v>
       </c>
       <c r="G50">
         <v>3.65</v>
@@ -5387,28 +5387,28 @@
         <v>25.5</v>
       </c>
       <c r="M50">
-        <v>15.47424</v>
+        <v>15.79662</v>
       </c>
       <c r="N50">
-        <v>10.02576</v>
+        <v>9.703379999999997</v>
       </c>
       <c r="O50">
-        <v>3.2082432</v>
+        <v>3.105081599999999</v>
       </c>
       <c r="P50">
-        <v>6.8175168</v>
+        <v>6.598298399999998</v>
       </c>
       <c r="Q50">
-        <v>15.3175168</v>
+        <v>15.0982984</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1621182026864682</v>
+        <v>0.1639505625271498</v>
       </c>
       <c r="T50">
-        <v>1.124885919932697</v>
+        <v>1.142606240032456</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.647899993796141</v>
+        <v>1.614269381677852</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1136027868888464</v>
+        <v>0.1135281083807293</v>
       </c>
       <c r="C51">
-        <v>202.3256059229957</v>
+        <v>199.1562000571797</v>
       </c>
       <c r="D51">
-        <v>374.1936059229957</v>
+        <v>374.6062000571797</v>
       </c>
       <c r="E51">
-        <v>138.918</v>
+        <v>142.5</v>
       </c>
       <c r="F51">
-        <v>175.518</v>
+        <v>179.1</v>
       </c>
       <c r="G51">
         <v>3.65</v>
@@ -5469,28 +5469,28 @@
         <v>25.5</v>
       </c>
       <c r="M51">
-        <v>15.79662</v>
+        <v>16.119</v>
       </c>
       <c r="N51">
-        <v>9.703379999999997</v>
+        <v>9.381</v>
       </c>
       <c r="O51">
-        <v>3.105081599999999</v>
+        <v>3.00192</v>
       </c>
       <c r="P51">
-        <v>6.598298399999998</v>
+        <v>6.37908</v>
       </c>
       <c r="Q51">
-        <v>15.0982984</v>
+        <v>14.87908</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1639505625271498</v>
+        <v>0.1658562167614586</v>
       </c>
       <c r="T51">
-        <v>1.142606240032456</v>
+        <v>1.161035372936206</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.614269381677852</v>
+        <v>1.581983994044295</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1135281083807293</v>
+        <v>0.1134534298726123</v>
       </c>
       <c r="C52">
-        <v>199.1562000571797</v>
+        <v>195.9877050665244</v>
       </c>
       <c r="D52">
-        <v>374.6062000571797</v>
+        <v>375.0197050665244</v>
       </c>
       <c r="E52">
-        <v>142.5</v>
+        <v>146.082</v>
       </c>
       <c r="F52">
-        <v>179.1</v>
+        <v>182.682</v>
       </c>
       <c r="G52">
         <v>3.65</v>
@@ -5551,28 +5551,28 @@
         <v>25.5</v>
       </c>
       <c r="M52">
-        <v>16.119</v>
+        <v>16.44138</v>
       </c>
       <c r="N52">
-        <v>9.381</v>
+        <v>9.058619999999998</v>
       </c>
       <c r="O52">
-        <v>3.00192</v>
+        <v>2.898758399999999</v>
       </c>
       <c r="P52">
-        <v>6.37908</v>
+        <v>6.159861599999998</v>
       </c>
       <c r="Q52">
-        <v>14.87908</v>
+        <v>14.6598616</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1658562167614586</v>
+        <v>0.1678396528012495</v>
       </c>
       <c r="T52">
-        <v>1.161035372936206</v>
+        <v>1.18021671534623</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.581983994044295</v>
+        <v>1.550964700043427</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1134534298726123</v>
+        <v>0.1133787513644952</v>
       </c>
       <c r="C53">
-        <v>195.9877050665244</v>
+        <v>192.8201239707418</v>
       </c>
       <c r="D53">
-        <v>375.0197050665244</v>
+        <v>375.4341239707419</v>
       </c>
       <c r="E53">
-        <v>146.082</v>
+        <v>149.664</v>
       </c>
       <c r="F53">
-        <v>182.682</v>
+        <v>186.264</v>
       </c>
       <c r="G53">
         <v>3.65</v>
@@ -5633,28 +5633,28 @@
         <v>25.5</v>
       </c>
       <c r="M53">
-        <v>16.44138</v>
+        <v>16.76376</v>
       </c>
       <c r="N53">
-        <v>9.058619999999998</v>
+        <v>8.736239999999999</v>
       </c>
       <c r="O53">
-        <v>2.898758399999999</v>
+        <v>2.7955968</v>
       </c>
       <c r="P53">
-        <v>6.159861599999998</v>
+        <v>5.940643199999998</v>
       </c>
       <c r="Q53">
-        <v>14.6598616</v>
+        <v>14.4406432</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1678396528012495</v>
+        <v>0.169905732009365</v>
       </c>
       <c r="T53">
-        <v>1.18021671534623</v>
+        <v>1.200197280356673</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.550964700043427</v>
+        <v>1.521138455811823</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1133787513644952</v>
+        <v>0.1369219150332162</v>
       </c>
       <c r="C54">
-        <v>192.8201239707418</v>
+        <v>92.23723209699145</v>
       </c>
       <c r="D54">
-        <v>375.4341239707419</v>
+        <v>278.4332320969915</v>
       </c>
       <c r="E54">
-        <v>149.664</v>
+        <v>153.246</v>
       </c>
       <c r="F54">
-        <v>186.264</v>
+        <v>189.846</v>
       </c>
       <c r="G54">
         <v>3.65</v>
@@ -5715,45 +5715,45 @@
         <v>25.5</v>
       </c>
       <c r="M54">
-        <v>16.76376</v>
+        <v>27.86939280000001</v>
       </c>
       <c r="N54">
-        <v>8.736239999999999</v>
+        <v>-2.369392800000007</v>
       </c>
       <c r="O54">
-        <v>2.7955968</v>
+        <v>-0.7582056960000023</v>
       </c>
       <c r="P54">
-        <v>5.940643199999998</v>
+        <v>-1.611187104000005</v>
       </c>
       <c r="Q54">
-        <v>14.4406432</v>
+        <v>6.888812895999996</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.169905732009365</v>
+        <v>0.1742520947818172</v>
       </c>
       <c r="T54">
-        <v>1.200197280356673</v>
+        <v>1.242229930214836</v>
       </c>
       <c r="U54">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.32</v>
+        <v>0.2927943230969854</v>
       </c>
       <c r="W54">
-        <v>0.06119999999999999</v>
+        <v>0.1038177933693626</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.521138455811823</v>
+        <v>0.9149822596780793</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1369219150332162</v>
+        <v>0.1379319150332162</v>
       </c>
       <c r="C55">
-        <v>92.23723209699145</v>
+        <v>85.60289605994538</v>
       </c>
       <c r="D55">
-        <v>278.4332320969915</v>
+        <v>275.3808960599454</v>
       </c>
       <c r="E55">
-        <v>153.246</v>
+        <v>156.828</v>
       </c>
       <c r="F55">
-        <v>189.846</v>
+        <v>193.428</v>
       </c>
       <c r="G55">
         <v>3.65</v>
@@ -5797,37 +5797,37 @@
         <v>25.5</v>
       </c>
       <c r="M55">
-        <v>27.86939280000001</v>
+        <v>28.39523040000001</v>
       </c>
       <c r="N55">
-        <v>-2.369392800000007</v>
+        <v>-2.895230400000006</v>
       </c>
       <c r="O55">
-        <v>-0.7582056960000023</v>
+        <v>-0.9264737280000021</v>
       </c>
       <c r="P55">
-        <v>-1.611187104000005</v>
+        <v>-1.968756672000004</v>
       </c>
       <c r="Q55">
-        <v>6.888812895999996</v>
+        <v>6.531243327999996</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1742520947818172</v>
+        <v>0.1770445316249002</v>
       </c>
       <c r="T55">
-        <v>1.242229930214836</v>
+        <v>1.269234928697767</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.2927943230969854</v>
+        <v>0.2873722060025968</v>
       </c>
       <c r="W55">
-        <v>0.1038177933693626</v>
+        <v>0.1046137601588188</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.9149822596780793</v>
+        <v>0.8980381437581149</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1379319150332162</v>
+        <v>0.1389419150332162</v>
       </c>
       <c r="C56">
-        <v>85.60289605994538</v>
+        <v>79.03475705988978</v>
       </c>
       <c r="D56">
-        <v>275.3808960599454</v>
+        <v>272.3947570598899</v>
       </c>
       <c r="E56">
-        <v>156.828</v>
+        <v>160.4100000000001</v>
       </c>
       <c r="F56">
-        <v>193.428</v>
+        <v>197.01</v>
       </c>
       <c r="G56">
         <v>3.65</v>
@@ -5879,37 +5879,37 @@
         <v>25.5</v>
       </c>
       <c r="M56">
-        <v>28.39523040000001</v>
+        <v>28.92106800000001</v>
       </c>
       <c r="N56">
-        <v>-2.895230400000006</v>
+        <v>-3.421068000000009</v>
       </c>
       <c r="O56">
-        <v>-0.9264737280000021</v>
+        <v>-1.094741760000003</v>
       </c>
       <c r="P56">
-        <v>-1.968756672000004</v>
+        <v>-2.326326240000006</v>
       </c>
       <c r="Q56">
-        <v>6.531243327999996</v>
+        <v>6.173673759999994</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1770445316249002</v>
+        <v>0.1799610767721202</v>
       </c>
       <c r="T56">
-        <v>1.269234928697767</v>
+        <v>1.297440149335495</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.2873722060025968</v>
+        <v>0.2821472568025495</v>
       </c>
       <c r="W56">
-        <v>0.1046137601588188</v>
+        <v>0.1053807827013857</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8980381437581149</v>
+        <v>0.8817101775079673</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1389419150332162</v>
+        <v>0.1399519150332162</v>
       </c>
       <c r="C57">
-        <v>79.03475705988978</v>
+        <v>72.53068474162171</v>
       </c>
       <c r="D57">
-        <v>272.3947570598899</v>
+        <v>269.4726847416218</v>
       </c>
       <c r="E57">
-        <v>160.4100000000001</v>
+        <v>163.992</v>
       </c>
       <c r="F57">
-        <v>197.01</v>
+        <v>200.592</v>
       </c>
       <c r="G57">
         <v>3.65</v>
@@ -5961,37 +5961,37 @@
         <v>25.5</v>
       </c>
       <c r="M57">
-        <v>28.92106800000001</v>
+        <v>29.44690560000001</v>
       </c>
       <c r="N57">
-        <v>-3.421068000000009</v>
+        <v>-3.946905600000008</v>
       </c>
       <c r="O57">
-        <v>-1.094741760000003</v>
+        <v>-1.263009792000003</v>
       </c>
       <c r="P57">
-        <v>-2.326326240000006</v>
+        <v>-2.683895808000005</v>
       </c>
       <c r="Q57">
-        <v>6.173673759999994</v>
+        <v>5.816104191999995</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1799610767721202</v>
+        <v>0.1830101921533047</v>
       </c>
       <c r="T57">
-        <v>1.297440149335495</v>
+        <v>1.326927425456756</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2821472568025495</v>
+        <v>0.2771089129310754</v>
       </c>
       <c r="W57">
-        <v>0.1053807827013857</v>
+        <v>0.1061204115817181</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8817101775079673</v>
+        <v>0.8659653529096107</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1399519150332162</v>
+        <v>0.1409619150332162</v>
       </c>
       <c r="C58">
-        <v>72.53068474162171</v>
+        <v>66.08863919194954</v>
       </c>
       <c r="D58">
-        <v>269.4726847416218</v>
+        <v>266.6126391919496</v>
       </c>
       <c r="E58">
-        <v>163.992</v>
+        <v>167.574</v>
       </c>
       <c r="F58">
-        <v>200.592</v>
+        <v>204.174</v>
       </c>
       <c r="G58">
         <v>3.65</v>
@@ -6043,37 +6043,37 @@
         <v>25.5</v>
       </c>
       <c r="M58">
-        <v>29.44690560000001</v>
+        <v>29.97274320000001</v>
       </c>
       <c r="N58">
-        <v>-3.946905600000008</v>
+        <v>-4.472743200000007</v>
       </c>
       <c r="O58">
-        <v>-1.263009792000003</v>
+        <v>-1.431277824000002</v>
       </c>
       <c r="P58">
-        <v>-2.683895808000005</v>
+        <v>-3.041465376000005</v>
       </c>
       <c r="Q58">
-        <v>5.816104191999995</v>
+        <v>5.458534623999995</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1830101921533047</v>
+        <v>0.1862011268545444</v>
       </c>
       <c r="T58">
-        <v>1.326927425456756</v>
+        <v>1.35778620279296</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2771089129310754</v>
+        <v>0.2722473530550917</v>
       </c>
       <c r="W58">
-        <v>0.1061204115817181</v>
+        <v>0.1068340885715125</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8659653529096107</v>
+        <v>0.8507729782971615</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1409619150332162</v>
+        <v>0.1419719150332162</v>
       </c>
       <c r="C59">
-        <v>66.08863919194954</v>
+        <v>59.70666619057099</v>
       </c>
       <c r="D59">
-        <v>266.6126391919496</v>
+        <v>263.8126661905711</v>
       </c>
       <c r="E59">
-        <v>167.574</v>
+        <v>171.1560000000001</v>
       </c>
       <c r="F59">
-        <v>204.174</v>
+        <v>207.7560000000001</v>
       </c>
       <c r="G59">
         <v>3.65</v>
@@ -6125,37 +6125,37 @@
         <v>25.5</v>
       </c>
       <c r="M59">
-        <v>29.97274320000001</v>
+        <v>30.49858080000001</v>
       </c>
       <c r="N59">
-        <v>-4.472743200000007</v>
+        <v>-4.99858080000001</v>
       </c>
       <c r="O59">
-        <v>-1.431277824000002</v>
+        <v>-1.599545856000003</v>
       </c>
       <c r="P59">
-        <v>-3.041465376000005</v>
+        <v>-3.399034944000006</v>
       </c>
       <c r="Q59">
-        <v>5.458534623999995</v>
+        <v>5.100965055999994</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1862011268545444</v>
+        <v>0.1895440108272717</v>
       </c>
       <c r="T59">
-        <v>1.35778620279296</v>
+        <v>1.390114445716602</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2722473530550917</v>
+        <v>0.2675534331748314</v>
       </c>
       <c r="W59">
-        <v>0.1068340885715125</v>
+        <v>0.1075231560099347</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8507729782971615</v>
+        <v>0.8361044786713483</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1419719150332162</v>
+        <v>0.1429819150332162</v>
       </c>
       <c r="C60">
-        <v>59.7066661905711</v>
+        <v>53.38289275709423</v>
       </c>
       <c r="D60">
-        <v>263.8126661905711</v>
+        <v>261.0708927570943</v>
       </c>
       <c r="E60">
-        <v>171.156</v>
+        <v>174.738</v>
       </c>
       <c r="F60">
-        <v>207.756</v>
+        <v>211.338</v>
       </c>
       <c r="G60">
         <v>3.65</v>
@@ -6207,37 +6207,37 @@
         <v>25.5</v>
       </c>
       <c r="M60">
-        <v>30.4985808</v>
+        <v>31.02441840000001</v>
       </c>
       <c r="N60">
-        <v>-4.998580800000003</v>
+        <v>-5.524418400000005</v>
       </c>
       <c r="O60">
-        <v>-1.599545856000001</v>
+        <v>-1.767813888000002</v>
       </c>
       <c r="P60">
-        <v>-3.399034944000002</v>
+        <v>-3.756604512000004</v>
       </c>
       <c r="Q60">
-        <v>5.100965055999998</v>
+        <v>4.743395487999996</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1895440108272716</v>
+        <v>0.1930499623108636</v>
       </c>
       <c r="T60">
-        <v>1.390114445716601</v>
+        <v>1.424019676099933</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2675534331748315</v>
+        <v>0.2630186292227157</v>
       </c>
       <c r="W60">
-        <v>0.1075231560099347</v>
+        <v>0.1081888652301053</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8361044786713485</v>
+        <v>0.8219332163209866</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1429819150332162</v>
+        <v>0.1439919150332162</v>
       </c>
       <c r="C61">
-        <v>53.38289275709423</v>
+        <v>47.11552297287659</v>
       </c>
       <c r="D61">
-        <v>261.0708927570943</v>
+        <v>258.3855229728766</v>
       </c>
       <c r="E61">
-        <v>174.738</v>
+        <v>178.32</v>
       </c>
       <c r="F61">
-        <v>211.338</v>
+        <v>214.92</v>
       </c>
       <c r="G61">
         <v>3.65</v>
@@ -6289,37 +6289,37 @@
         <v>25.5</v>
       </c>
       <c r="M61">
-        <v>31.02441840000001</v>
+        <v>31.550256</v>
       </c>
       <c r="N61">
-        <v>-5.524418400000005</v>
+        <v>-6.050256000000005</v>
       </c>
       <c r="O61">
-        <v>-1.767813888000002</v>
+        <v>-1.936081920000001</v>
       </c>
       <c r="P61">
-        <v>-3.756604512000004</v>
+        <v>-4.114174080000003</v>
       </c>
       <c r="Q61">
-        <v>4.743395487999996</v>
+        <v>4.385825919999997</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1930499623108636</v>
+        <v>0.1967312113686352</v>
       </c>
       <c r="T61">
-        <v>1.424019676099933</v>
+        <v>1.459620168002432</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2630186292227157</v>
+        <v>0.2586349854023371</v>
       </c>
       <c r="W61">
-        <v>0.1081888652301053</v>
+        <v>0.1088323841429369</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8219332163209866</v>
+        <v>0.8082343293823034</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1439919150332162</v>
+        <v>0.1809241643305914</v>
       </c>
       <c r="C62">
-        <v>47.11552297287659</v>
+        <v>-27.08862367677719</v>
       </c>
       <c r="D62">
-        <v>258.3855229728766</v>
+        <v>187.7633763232228</v>
       </c>
       <c r="E62">
-        <v>178.32</v>
+        <v>181.902</v>
       </c>
       <c r="F62">
-        <v>214.92</v>
+        <v>218.502</v>
       </c>
       <c r="G62">
         <v>3.65</v>
@@ -6371,45 +6371,45 @@
         <v>25.5</v>
       </c>
       <c r="M62">
-        <v>31.550256</v>
+        <v>43.8752016</v>
       </c>
       <c r="N62">
-        <v>-6.050256000000005</v>
+        <v>-18.3752016</v>
       </c>
       <c r="O62">
-        <v>-1.936081920000001</v>
+        <v>-5.880064512000001</v>
       </c>
       <c r="P62">
-        <v>-4.114174080000003</v>
+        <v>-12.495137088</v>
       </c>
       <c r="Q62">
-        <v>4.385825919999997</v>
+        <v>-3.995137088000003</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1967312113686352</v>
+        <v>0.2082480354995622</v>
       </c>
       <c r="T62">
-        <v>1.459620168002432</v>
+        <v>1.570996659454427</v>
       </c>
       <c r="U62">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.2586349854023371</v>
+        <v>0.1859820514192235</v>
       </c>
       <c r="W62">
-        <v>0.1088323841429369</v>
+        <v>0.1634548040750199</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.8082343293823034</v>
+        <v>0.5811939106850736</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1809241643305914</v>
+        <v>0.1824741643305914</v>
       </c>
       <c r="C63">
-        <v>-27.08862367677719</v>
+        <v>-32.80001831933035</v>
       </c>
       <c r="D63">
-        <v>187.7633763232228</v>
+        <v>185.6339816806697</v>
       </c>
       <c r="E63">
-        <v>181.902</v>
+        <v>185.484</v>
       </c>
       <c r="F63">
-        <v>218.502</v>
+        <v>222.084</v>
       </c>
       <c r="G63">
         <v>3.65</v>
@@ -6453,37 +6453,37 @@
         <v>25.5</v>
       </c>
       <c r="M63">
-        <v>43.8752016</v>
+        <v>44.59446720000001</v>
       </c>
       <c r="N63">
-        <v>-18.3752016</v>
+        <v>-19.09446720000001</v>
       </c>
       <c r="O63">
-        <v>-5.880064512000001</v>
+        <v>-6.110229504000004</v>
       </c>
       <c r="P63">
-        <v>-12.495137088</v>
+        <v>-12.98423769600001</v>
       </c>
       <c r="Q63">
-        <v>-3.995137088000003</v>
+        <v>-4.484237696000008</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2082480354995622</v>
+        <v>0.2125229838021822</v>
       </c>
       <c r="T63">
-        <v>1.570996659454427</v>
+        <v>1.612338676808491</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1859820514192235</v>
+        <v>0.1829823409124619</v>
       </c>
       <c r="W63">
-        <v>0.1634548040750199</v>
+        <v>0.1640571459447777</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5811939106850736</v>
+        <v>0.5718198153514433</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1824741643305914</v>
+        <v>0.1840241643305914</v>
       </c>
       <c r="C64">
-        <v>-32.80001831933035</v>
+        <v>-38.4636563093193</v>
       </c>
       <c r="D64">
-        <v>185.6339816806697</v>
+        <v>183.5523436906807</v>
       </c>
       <c r="E64">
-        <v>185.484</v>
+        <v>189.066</v>
       </c>
       <c r="F64">
-        <v>222.084</v>
+        <v>225.666</v>
       </c>
       <c r="G64">
         <v>3.65</v>
@@ -6535,37 +6535,37 @@
         <v>25.5</v>
       </c>
       <c r="M64">
-        <v>44.59446720000001</v>
+        <v>45.3137328</v>
       </c>
       <c r="N64">
-        <v>-19.09446720000001</v>
+        <v>-19.8137328</v>
       </c>
       <c r="O64">
-        <v>-6.110229504000004</v>
+        <v>-6.340394496000002</v>
       </c>
       <c r="P64">
-        <v>-12.98423769600001</v>
+        <v>-13.473338304</v>
       </c>
       <c r="Q64">
-        <v>-4.484237696000008</v>
+        <v>-4.973338304000002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2125229838021822</v>
+        <v>0.2170290103914304</v>
       </c>
       <c r="T64">
-        <v>1.612338676808491</v>
+        <v>1.655915397803315</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1829823409124619</v>
+        <v>0.1800778593106768</v>
       </c>
       <c r="W64">
-        <v>0.1640571459447777</v>
+        <v>0.1646403658504161</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5718198153514433</v>
+        <v>0.5627433103458649</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1840241643305914</v>
+        <v>0.1855741643305914</v>
       </c>
       <c r="C65">
-        <v>-38.4636563093193</v>
+        <v>-44.08112641270449</v>
       </c>
       <c r="D65">
-        <v>183.5523436906807</v>
+        <v>181.5168735872955</v>
       </c>
       <c r="E65">
-        <v>189.066</v>
+        <v>192.6480000000001</v>
       </c>
       <c r="F65">
-        <v>225.666</v>
+        <v>229.248</v>
       </c>
       <c r="G65">
         <v>3.65</v>
@@ -6617,37 +6617,37 @@
         <v>25.5</v>
       </c>
       <c r="M65">
-        <v>45.3137328</v>
+        <v>46.03299840000001</v>
       </c>
       <c r="N65">
-        <v>-19.8137328</v>
+        <v>-20.53299840000001</v>
       </c>
       <c r="O65">
-        <v>-6.340394496000002</v>
+        <v>-6.570559488000003</v>
       </c>
       <c r="P65">
-        <v>-13.473338304</v>
+        <v>-13.96243891200001</v>
       </c>
       <c r="Q65">
-        <v>-4.973338304000002</v>
+        <v>-5.462438912000007</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2170290103914304</v>
+        <v>0.2217853717911924</v>
       </c>
       <c r="T65">
-        <v>1.655915397803315</v>
+        <v>1.701913047742296</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1800778593106768</v>
+        <v>0.1772641427589474</v>
       </c>
       <c r="W65">
-        <v>0.1646403658504161</v>
+        <v>0.1652053601340034</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5627433103458649</v>
+        <v>0.5539504461217106</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1855741643305914</v>
+        <v>0.1871241643305914</v>
       </c>
       <c r="C66">
-        <v>-44.08112641270449</v>
+        <v>-49.653947695059</v>
       </c>
       <c r="D66">
-        <v>181.5168735872955</v>
+        <v>179.526052304941</v>
       </c>
       <c r="E66">
-        <v>192.6480000000001</v>
+        <v>196.23</v>
       </c>
       <c r="F66">
-        <v>229.248</v>
+        <v>232.83</v>
       </c>
       <c r="G66">
         <v>3.65</v>
@@ -6699,37 +6699,37 @@
         <v>25.5</v>
       </c>
       <c r="M66">
-        <v>46.03299840000001</v>
+        <v>46.75226400000001</v>
       </c>
       <c r="N66">
-        <v>-20.53299840000001</v>
+        <v>-21.25226400000001</v>
       </c>
       <c r="O66">
-        <v>-6.570559488000003</v>
+        <v>-6.800724480000004</v>
       </c>
       <c r="P66">
-        <v>-13.96243891200001</v>
+        <v>-14.45153952000001</v>
       </c>
       <c r="Q66">
-        <v>-5.462438912000007</v>
+        <v>-5.951539520000008</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2217853717911924</v>
+        <v>0.2268135252709408</v>
       </c>
       <c r="T66">
-        <v>1.701913047742296</v>
+        <v>1.750539134820648</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1772641427589474</v>
+        <v>0.1745370021011174</v>
       </c>
       <c r="W66">
-        <v>0.1652053601340034</v>
+        <v>0.1657529699780956</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5539504461217106</v>
+        <v>0.5454281315659921</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1871241643305914</v>
+        <v>0.1886741643305914</v>
       </c>
       <c r="C67">
-        <v>-49.653947695059</v>
+        <v>-55.18357330236464</v>
       </c>
       <c r="D67">
-        <v>179.526052304941</v>
+        <v>177.5784266976354</v>
       </c>
       <c r="E67">
-        <v>196.23</v>
+        <v>199.812</v>
       </c>
       <c r="F67">
-        <v>232.83</v>
+        <v>236.412</v>
       </c>
       <c r="G67">
         <v>3.65</v>
@@ -6781,37 +6781,37 @@
         <v>25.5</v>
       </c>
       <c r="M67">
-        <v>46.75226400000001</v>
+        <v>47.47152960000001</v>
       </c>
       <c r="N67">
-        <v>-21.25226400000001</v>
+        <v>-21.97152960000001</v>
       </c>
       <c r="O67">
-        <v>-6.800724480000004</v>
+        <v>-7.030889472000004</v>
       </c>
       <c r="P67">
-        <v>-14.45153952000001</v>
+        <v>-14.94064012800001</v>
       </c>
       <c r="Q67">
-        <v>-5.951539520000008</v>
+        <v>-6.440640128000007</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2268135252709408</v>
+        <v>0.232137452484792</v>
       </c>
       <c r="T67">
-        <v>1.750539134820648</v>
+        <v>1.802025579962432</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1745370021011174</v>
+        <v>0.1718925020692824</v>
       </c>
       <c r="W67">
-        <v>0.1657529699780956</v>
+        <v>0.1662839855844881</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5454281315659921</v>
+        <v>0.5371640689665074</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1886741643305914</v>
+        <v>0.1902241643305914</v>
       </c>
       <c r="C68">
-        <v>-55.18357330236464</v>
+        <v>-60.67139399834798</v>
       </c>
       <c r="D68">
-        <v>177.5784266976354</v>
+        <v>175.6726060016521</v>
       </c>
       <c r="E68">
-        <v>199.812</v>
+        <v>203.3940000000001</v>
       </c>
       <c r="F68">
-        <v>236.412</v>
+        <v>239.9940000000001</v>
       </c>
       <c r="G68">
         <v>3.65</v>
@@ -6863,37 +6863,37 @@
         <v>25.5</v>
       </c>
       <c r="M68">
-        <v>47.47152960000001</v>
+        <v>48.19079520000001</v>
       </c>
       <c r="N68">
-        <v>-21.97152960000001</v>
+        <v>-22.69079520000001</v>
       </c>
       <c r="O68">
-        <v>-7.030889472000004</v>
+        <v>-7.261054464000003</v>
       </c>
       <c r="P68">
-        <v>-14.94064012800001</v>
+        <v>-15.42974073600001</v>
       </c>
       <c r="Q68">
-        <v>-6.440640128000007</v>
+        <v>-6.929740736000007</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.232137452484792</v>
+        <v>0.2377840419540281</v>
       </c>
       <c r="T68">
-        <v>1.802025579962432</v>
+        <v>1.856632415718869</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1718925020692824</v>
+        <v>0.169326942336905</v>
       </c>
       <c r="W68">
-        <v>0.1662839855844881</v>
+        <v>0.1667991499787495</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5371640689665074</v>
+        <v>0.5291466948028281</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1902241643305914</v>
+        <v>0.1917741643305914</v>
       </c>
       <c r="C69">
-        <v>-60.67139399834798</v>
+        <v>-66.11874147645301</v>
       </c>
       <c r="D69">
-        <v>175.6726060016521</v>
+        <v>173.807258523547</v>
       </c>
       <c r="E69">
-        <v>203.3940000000001</v>
+        <v>206.9760000000001</v>
       </c>
       <c r="F69">
-        <v>239.9940000000001</v>
+        <v>243.5760000000001</v>
       </c>
       <c r="G69">
         <v>3.65</v>
@@ -6945,37 +6945,37 @@
         <v>25.5</v>
       </c>
       <c r="M69">
-        <v>48.19079520000001</v>
+        <v>48.91006080000001</v>
       </c>
       <c r="N69">
-        <v>-22.69079520000001</v>
+        <v>-23.41006080000001</v>
       </c>
       <c r="O69">
-        <v>-7.261054464000003</v>
+        <v>-7.491219456000003</v>
       </c>
       <c r="P69">
-        <v>-15.42974073600001</v>
+        <v>-15.91884134400001</v>
       </c>
       <c r="Q69">
-        <v>-6.929740736000007</v>
+        <v>-7.418841344000008</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2377840419540281</v>
+        <v>0.2437835432650914</v>
       </c>
       <c r="T69">
-        <v>1.856632415718869</v>
+        <v>1.914652178710083</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.169326942336905</v>
+        <v>0.1668368402437152</v>
       </c>
       <c r="W69">
-        <v>0.1667991499787495</v>
+        <v>0.167299162479062</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5291466948028281</v>
+        <v>0.5213651257616101</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1917741643305914</v>
+        <v>0.1933241643305914</v>
       </c>
       <c r="C70">
-        <v>-66.11874147645301</v>
+        <v>-71.52689146302598</v>
       </c>
       <c r="D70">
-        <v>173.807258523547</v>
+        <v>171.9811085369741</v>
       </c>
       <c r="E70">
-        <v>206.9760000000001</v>
+        <v>210.558</v>
       </c>
       <c r="F70">
-        <v>243.5760000000001</v>
+        <v>247.158</v>
       </c>
       <c r="G70">
         <v>3.65</v>
@@ -7027,37 +7027,37 @@
         <v>25.5</v>
       </c>
       <c r="M70">
-        <v>48.91006080000001</v>
+        <v>49.62932640000001</v>
       </c>
       <c r="N70">
-        <v>-23.41006080000001</v>
+        <v>-24.12932640000001</v>
       </c>
       <c r="O70">
-        <v>-7.491219456000003</v>
+        <v>-7.721384448000004</v>
       </c>
       <c r="P70">
-        <v>-15.91884134400001</v>
+        <v>-16.40794195200001</v>
       </c>
       <c r="Q70">
-        <v>-7.418841344000008</v>
+        <v>-7.907941952000009</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2437835432650914</v>
+        <v>0.2501701091768686</v>
       </c>
       <c r="T70">
-        <v>1.914652178710083</v>
+        <v>1.97641515221686</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1668368402437152</v>
+        <v>0.1644189150227918</v>
       </c>
       <c r="W70">
-        <v>0.167299162479062</v>
+        <v>0.1677846818634234</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5213651257616101</v>
+        <v>0.5138091094462245</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1933241643305914</v>
+        <v>0.1948741643305914</v>
       </c>
       <c r="C71">
-        <v>-71.52689146302598</v>
+        <v>-76.89706662690719</v>
       </c>
       <c r="D71">
-        <v>171.9811085369741</v>
+        <v>170.1929333730929</v>
       </c>
       <c r="E71">
-        <v>210.558</v>
+        <v>214.1400000000001</v>
       </c>
       <c r="F71">
-        <v>247.158</v>
+        <v>250.7400000000001</v>
       </c>
       <c r="G71">
         <v>3.65</v>
@@ -7109,37 +7109,37 @@
         <v>25.5</v>
       </c>
       <c r="M71">
-        <v>49.62932640000001</v>
+        <v>50.34859200000002</v>
       </c>
       <c r="N71">
-        <v>-24.12932640000001</v>
+        <v>-24.84859200000002</v>
       </c>
       <c r="O71">
-        <v>-7.721384448000004</v>
+        <v>-7.951549440000006</v>
       </c>
       <c r="P71">
-        <v>-16.40794195200001</v>
+        <v>-16.89704256000001</v>
       </c>
       <c r="Q71">
-        <v>-7.907941952000009</v>
+        <v>-8.39704256000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2501701091768686</v>
+        <v>0.2569824461494308</v>
       </c>
       <c r="T71">
-        <v>1.97641515221686</v>
+        <v>2.042295657290755</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1644189150227918</v>
+        <v>0.1620700733796091</v>
       </c>
       <c r="W71">
-        <v>0.1677846818634234</v>
+        <v>0.1682563292653745</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5138091094462245</v>
+        <v>0.5064689793112782</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1948741643305914</v>
+        <v>0.2224775379436591</v>
       </c>
       <c r="C72">
-        <v>-76.89706662690719</v>
+        <v>-107.0693122284705</v>
       </c>
       <c r="D72">
-        <v>170.1929333730929</v>
+        <v>143.6026877715295</v>
       </c>
       <c r="E72">
-        <v>214.1400000000001</v>
+        <v>217.7220000000001</v>
       </c>
       <c r="F72">
-        <v>250.7400000000001</v>
+        <v>254.3220000000001</v>
       </c>
       <c r="G72">
         <v>3.65</v>
@@ -7191,45 +7191,45 @@
         <v>25.5</v>
       </c>
       <c r="M72">
-        <v>50.34859200000002</v>
+        <v>59.96912760000001</v>
       </c>
       <c r="N72">
-        <v>-24.84859200000002</v>
+        <v>-34.46912760000001</v>
       </c>
       <c r="O72">
-        <v>-7.951549440000006</v>
+        <v>-11.03012083200001</v>
       </c>
       <c r="P72">
-        <v>-16.89704256000001</v>
+        <v>-23.43900676800001</v>
       </c>
       <c r="Q72">
-        <v>-8.39704256000001</v>
+        <v>-14.93900676800001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2569824461494308</v>
+        <v>0.2684141636479206</v>
       </c>
       <c r="T72">
-        <v>2.042295657290755</v>
+        <v>2.152849102561582</v>
       </c>
       <c r="U72">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1620700733796091</v>
+        <v>0.1360700134647281</v>
       </c>
       <c r="W72">
-        <v>0.1682563292653745</v>
+        <v>0.2037146908250171</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.5064689793112782</v>
+        <v>0.4252187920772753</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2224775379436591</v>
+        <v>0.2243775379436591</v>
       </c>
       <c r="C73">
-        <v>-107.0693122284705</v>
+        <v>-112.1791925537776</v>
       </c>
       <c r="D73">
-        <v>143.6026877715295</v>
+        <v>142.0748074462224</v>
       </c>
       <c r="E73">
-        <v>217.722</v>
+        <v>221.304</v>
       </c>
       <c r="F73">
-        <v>254.322</v>
+        <v>257.904</v>
       </c>
       <c r="G73">
         <v>3.65</v>
@@ -7273,37 +7273,37 @@
         <v>25.5</v>
       </c>
       <c r="M73">
-        <v>59.96912760000001</v>
+        <v>60.8137632</v>
       </c>
       <c r="N73">
-        <v>-34.46912760000001</v>
+        <v>-35.3137632</v>
       </c>
       <c r="O73">
-        <v>-11.030120832</v>
+        <v>-11.300404224</v>
       </c>
       <c r="P73">
-        <v>-23.43900676800001</v>
+        <v>-24.013358976</v>
       </c>
       <c r="Q73">
-        <v>-14.93900676800001</v>
+        <v>-15.513358976</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2684141636479205</v>
+        <v>0.2763646694924891</v>
       </c>
       <c r="T73">
-        <v>2.152849102561581</v>
+        <v>2.229736570510209</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.1360700134647281</v>
+        <v>0.1341801521666069</v>
       </c>
       <c r="W73">
-        <v>0.2037146908250171</v>
+        <v>0.2041603201191141</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4252187920772754</v>
+        <v>0.4193129755206466</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2243775379436591</v>
+        <v>0.2262775379436591</v>
       </c>
       <c r="C74">
-        <v>-112.1791925537776</v>
+        <v>-117.256902974163</v>
       </c>
       <c r="D74">
-        <v>142.0748074462224</v>
+        <v>140.579097025837</v>
       </c>
       <c r="E74">
-        <v>221.304</v>
+        <v>224.8860000000001</v>
       </c>
       <c r="F74">
-        <v>257.904</v>
+        <v>261.486</v>
       </c>
       <c r="G74">
         <v>3.65</v>
@@ -7355,37 +7355,37 @@
         <v>25.5</v>
       </c>
       <c r="M74">
-        <v>60.8137632</v>
+        <v>61.65839880000001</v>
       </c>
       <c r="N74">
-        <v>-35.3137632</v>
+        <v>-36.15839880000001</v>
       </c>
       <c r="O74">
-        <v>-11.300404224</v>
+        <v>-11.570687616</v>
       </c>
       <c r="P74">
-        <v>-24.013358976</v>
+        <v>-24.58771118400001</v>
       </c>
       <c r="Q74">
-        <v>-15.513358976</v>
+        <v>-16.08771118400001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2763646694924891</v>
+        <v>0.2849041016959146</v>
       </c>
       <c r="T74">
-        <v>2.229736570510209</v>
+        <v>2.312319406455031</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1341801521666069</v>
+        <v>0.132342067890352</v>
       </c>
       <c r="W74">
-        <v>0.2041603201191141</v>
+        <v>0.204593740391455</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4193129755206466</v>
+        <v>0.41356896215735</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2262775379436591</v>
+        <v>0.2281775379436591</v>
       </c>
       <c r="C75">
-        <v>-117.256902974163</v>
+        <v>-122.3034489229717</v>
       </c>
       <c r="D75">
-        <v>140.579097025837</v>
+        <v>139.1145510770284</v>
       </c>
       <c r="E75">
-        <v>224.8860000000001</v>
+        <v>228.468</v>
       </c>
       <c r="F75">
-        <v>261.486</v>
+        <v>265.068</v>
       </c>
       <c r="G75">
         <v>3.65</v>
@@ -7437,37 +7437,37 @@
         <v>25.5</v>
       </c>
       <c r="M75">
-        <v>61.65839880000001</v>
+        <v>62.50303440000001</v>
       </c>
       <c r="N75">
-        <v>-36.15839880000001</v>
+        <v>-37.00303440000001</v>
       </c>
       <c r="O75">
-        <v>-11.570687616</v>
+        <v>-11.840971008</v>
       </c>
       <c r="P75">
-        <v>-24.58771118400001</v>
+        <v>-25.16206339200001</v>
       </c>
       <c r="Q75">
-        <v>-16.08771118400001</v>
+        <v>-16.66206339200001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2849041016959146</v>
+        <v>0.2941004132996036</v>
       </c>
       <c r="T75">
-        <v>2.312319406455031</v>
+        <v>2.401254768241763</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.132342067890352</v>
+        <v>0.1305536615675094</v>
       </c>
       <c r="W75">
-        <v>0.204593740391455</v>
+        <v>0.2050154466023813</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.41356896215735</v>
+        <v>0.4079801923984669</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2281775379436591</v>
+        <v>0.2300775379436591</v>
       </c>
       <c r="C76">
-        <v>-122.3034489229717</v>
+        <v>-127.3197943673262</v>
       </c>
       <c r="D76">
-        <v>139.1145510770284</v>
+        <v>137.6802056326738</v>
       </c>
       <c r="E76">
-        <v>228.468</v>
+        <v>232.05</v>
       </c>
       <c r="F76">
-        <v>265.068</v>
+        <v>268.65</v>
       </c>
       <c r="G76">
         <v>3.65</v>
@@ -7519,37 +7519,37 @@
         <v>25.5</v>
       </c>
       <c r="M76">
-        <v>62.50303440000001</v>
+        <v>63.34767000000001</v>
       </c>
       <c r="N76">
-        <v>-37.00303440000001</v>
+        <v>-37.84767000000001</v>
       </c>
       <c r="O76">
-        <v>-11.840971008</v>
+        <v>-12.1112544</v>
       </c>
       <c r="P76">
-        <v>-25.16206339200001</v>
+        <v>-25.7364156</v>
       </c>
       <c r="Q76">
-        <v>-16.66206339200001</v>
+        <v>-17.2364156</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2941004132996036</v>
+        <v>0.3040324298315878</v>
       </c>
       <c r="T76">
-        <v>2.401254768241763</v>
+        <v>2.497304958971434</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1305536615675094</v>
+        <v>0.1288129460799426</v>
       </c>
       <c r="W76">
-        <v>0.2050154466023813</v>
+        <v>0.2054259073143495</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4079801923984669</v>
+        <v>0.4025404564998207</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2300775379436591</v>
+        <v>0.2319775379436591</v>
       </c>
       <c r="C77">
-        <v>-127.3197943673262</v>
+        <v>-132.3068639240052</v>
       </c>
       <c r="D77">
-        <v>137.6802056326738</v>
+        <v>136.2751360759948</v>
       </c>
       <c r="E77">
-        <v>232.05</v>
+        <v>235.632</v>
       </c>
       <c r="F77">
-        <v>268.65</v>
+        <v>272.232</v>
       </c>
       <c r="G77">
         <v>3.65</v>
@@ -7601,37 +7601,37 @@
         <v>25.5</v>
       </c>
       <c r="M77">
-        <v>63.34767000000001</v>
+        <v>64.19230560000001</v>
       </c>
       <c r="N77">
-        <v>-37.84767000000001</v>
+        <v>-38.69230560000001</v>
       </c>
       <c r="O77">
-        <v>-12.1112544</v>
+        <v>-12.381537792</v>
       </c>
       <c r="P77">
-        <v>-25.7364156</v>
+        <v>-26.31076780800001</v>
       </c>
       <c r="Q77">
-        <v>-17.2364156</v>
+        <v>-17.81076780800001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3040324298315878</v>
+        <v>0.314792114407904</v>
       </c>
       <c r="T77">
-        <v>2.497304958971434</v>
+        <v>2.601359332261911</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1288129460799426</v>
+        <v>0.1271180388946802</v>
       </c>
       <c r="W77">
-        <v>0.2054259073143495</v>
+        <v>0.2058255664286344</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4025404564998207</v>
+        <v>0.3972438715458757</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2319775379436591</v>
+        <v>0.2338775379436591</v>
       </c>
       <c r="C78">
-        <v>-132.3068639240052</v>
+        <v>-137.2655448470719</v>
       </c>
       <c r="D78">
-        <v>136.2751360759948</v>
+        <v>134.8984551529281</v>
       </c>
       <c r="E78">
-        <v>235.632</v>
+        <v>239.214</v>
       </c>
       <c r="F78">
-        <v>272.232</v>
+        <v>275.814</v>
       </c>
       <c r="G78">
         <v>3.65</v>
@@ -7683,37 +7683,37 @@
         <v>25.5</v>
       </c>
       <c r="M78">
-        <v>64.19230560000001</v>
+        <v>65.0369412</v>
       </c>
       <c r="N78">
-        <v>-38.69230560000001</v>
+        <v>-39.5369412</v>
       </c>
       <c r="O78">
-        <v>-12.381537792</v>
+        <v>-12.651821184</v>
       </c>
       <c r="P78">
-        <v>-26.31076780800001</v>
+        <v>-26.885120016</v>
       </c>
       <c r="Q78">
-        <v>-17.81076780800001</v>
+        <v>-18.385120016</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.314792114407904</v>
+        <v>0.3264874237299868</v>
       </c>
       <c r="T78">
-        <v>2.601359332261911</v>
+        <v>2.714461911925472</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1271180388946802</v>
+        <v>0.1254671552726714</v>
       </c>
       <c r="W78">
-        <v>0.2058255664286344</v>
+        <v>0.2062148447867041</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3972438715458757</v>
+        <v>0.3920848602270981</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2338775379436591</v>
+        <v>0.2357775379436591</v>
       </c>
       <c r="C79">
-        <v>-137.2655448470719</v>
+        <v>-142.1966888962309</v>
       </c>
       <c r="D79">
-        <v>134.8984551529281</v>
+        <v>133.5493111037691</v>
       </c>
       <c r="E79">
-        <v>239.214</v>
+        <v>242.7960000000001</v>
       </c>
       <c r="F79">
-        <v>275.814</v>
+        <v>279.3960000000001</v>
       </c>
       <c r="G79">
         <v>3.65</v>
@@ -7765,37 +7765,37 @@
         <v>25.5</v>
       </c>
       <c r="M79">
-        <v>65.0369412</v>
+        <v>65.88157680000002</v>
       </c>
       <c r="N79">
-        <v>-39.5369412</v>
+        <v>-40.38157680000002</v>
       </c>
       <c r="O79">
-        <v>-12.651821184</v>
+        <v>-12.92210457600001</v>
       </c>
       <c r="P79">
-        <v>-26.885120016</v>
+        <v>-27.45947222400001</v>
       </c>
       <c r="Q79">
-        <v>-18.385120016</v>
+        <v>-18.95947222400001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3264874237299868</v>
+        <v>0.3392459429904408</v>
       </c>
       <c r="T79">
-        <v>2.714461911925472</v>
+        <v>2.837846544285721</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1254671552726714</v>
+        <v>0.1238586019999448</v>
       </c>
       <c r="W79">
-        <v>0.2062148447867041</v>
+        <v>0.206594141648413</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3920848602270981</v>
+        <v>0.3870581312498276</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2357775379436591</v>
+        <v>0.2376775379436591</v>
       </c>
       <c r="C80">
-        <v>-142.1966888962309</v>
+        <v>-147.1011140941802</v>
       </c>
       <c r="D80">
-        <v>133.5493111037691</v>
+        <v>132.2268859058199</v>
       </c>
       <c r="E80">
-        <v>242.7960000000001</v>
+        <v>246.3780000000001</v>
       </c>
       <c r="F80">
-        <v>279.3960000000001</v>
+        <v>282.9780000000001</v>
       </c>
       <c r="G80">
         <v>3.65</v>
@@ -7847,37 +7847,37 @@
         <v>25.5</v>
       </c>
       <c r="M80">
-        <v>65.88157680000002</v>
+        <v>66.72621240000002</v>
       </c>
       <c r="N80">
-        <v>-40.38157680000002</v>
+        <v>-41.22621240000002</v>
       </c>
       <c r="O80">
-        <v>-12.92210457600001</v>
+        <v>-13.19238796800001</v>
       </c>
       <c r="P80">
-        <v>-27.45947222400001</v>
+        <v>-28.03382443200002</v>
       </c>
       <c r="Q80">
-        <v>-18.95947222400001</v>
+        <v>-19.53382443200002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3392459429904408</v>
+        <v>0.3532195593233189</v>
       </c>
       <c r="T80">
-        <v>2.837846544285721</v>
+        <v>2.972982094013613</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1238586019999448</v>
+        <v>0.1222907715948822</v>
       </c>
       <c r="W80">
-        <v>0.206594141648413</v>
+        <v>0.2069638360579268</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3870581312498276</v>
+        <v>0.3821586612340069</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2376775379436591</v>
+        <v>0.2395775379436591</v>
       </c>
       <c r="C81">
-        <v>-147.1011140941802</v>
+        <v>-151.9796063805777</v>
       </c>
       <c r="D81">
-        <v>132.2268859058199</v>
+        <v>130.9303936194224</v>
       </c>
       <c r="E81">
-        <v>246.3780000000001</v>
+        <v>249.9600000000001</v>
       </c>
       <c r="F81">
-        <v>282.9780000000001</v>
+        <v>286.5600000000001</v>
       </c>
       <c r="G81">
         <v>3.65</v>
@@ -7929,37 +7929,37 @@
         <v>25.5</v>
       </c>
       <c r="M81">
-        <v>66.72621240000002</v>
+        <v>67.57084800000001</v>
       </c>
       <c r="N81">
-        <v>-41.22621240000002</v>
+        <v>-42.07084800000001</v>
       </c>
       <c r="O81">
-        <v>-13.19238796800001</v>
+        <v>-13.46267136</v>
       </c>
       <c r="P81">
-        <v>-28.03382443200002</v>
+        <v>-28.60817664000001</v>
       </c>
       <c r="Q81">
-        <v>-19.53382443200002</v>
+        <v>-20.10817664000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3532195593233189</v>
+        <v>0.3685905372894849</v>
       </c>
       <c r="T81">
-        <v>2.972982094013613</v>
+        <v>3.121631198714293</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1222907715948822</v>
+        <v>0.1207621369499462</v>
       </c>
       <c r="W81">
-        <v>0.2069638360579268</v>
+        <v>0.2073242881072027</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3821586612340069</v>
+        <v>0.3773816779685819</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2395775379436591</v>
+        <v>0.2414775379436591</v>
       </c>
       <c r="C82">
-        <v>-151.9796063805777</v>
+        <v>-156.8329211696494</v>
       </c>
       <c r="D82">
-        <v>130.9303936194224</v>
+        <v>129.6590788303507</v>
       </c>
       <c r="E82">
-        <v>249.9600000000001</v>
+        <v>253.5420000000001</v>
       </c>
       <c r="F82">
-        <v>286.5600000000001</v>
+        <v>290.1420000000001</v>
       </c>
       <c r="G82">
         <v>3.65</v>
@@ -8011,37 +8011,37 @@
         <v>25.5</v>
       </c>
       <c r="M82">
-        <v>67.57084800000001</v>
+        <v>68.41548360000002</v>
       </c>
       <c r="N82">
-        <v>-42.07084800000001</v>
+        <v>-42.91548360000002</v>
       </c>
       <c r="O82">
-        <v>-13.46267136</v>
+        <v>-13.732954752</v>
       </c>
       <c r="P82">
-        <v>-28.60817664000001</v>
+        <v>-29.18252884800001</v>
       </c>
       <c r="Q82">
-        <v>-20.10817664000001</v>
+        <v>-20.68252884800001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3685905372894849</v>
+        <v>0.3855795129362998</v>
       </c>
       <c r="T82">
-        <v>3.121631198714293</v>
+        <v>3.285927577593993</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1207621369499462</v>
+        <v>0.1192712463703172</v>
       </c>
       <c r="W82">
-        <v>0.2073242881072027</v>
+        <v>0.2076758401058792</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3773816779685819</v>
+        <v>0.3727226449072414</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2414775379436591</v>
+        <v>0.2433775379436591</v>
       </c>
       <c r="C83">
-        <v>-156.8329211696494</v>
+        <v>-161.6617848179245</v>
       </c>
       <c r="D83">
-        <v>129.6590788303507</v>
+        <v>128.4122151820755</v>
       </c>
       <c r="E83">
-        <v>253.5420000000001</v>
+        <v>257.124</v>
       </c>
       <c r="F83">
-        <v>290.1420000000001</v>
+        <v>293.724</v>
       </c>
       <c r="G83">
         <v>3.65</v>
@@ -8093,37 +8093,37 @@
         <v>25.5</v>
       </c>
       <c r="M83">
-        <v>68.41548360000002</v>
+        <v>69.26011920000002</v>
       </c>
       <c r="N83">
-        <v>-42.91548360000002</v>
+        <v>-43.76011920000002</v>
       </c>
       <c r="O83">
-        <v>-13.732954752</v>
+        <v>-14.00323814400001</v>
       </c>
       <c r="P83">
-        <v>-29.18252884800001</v>
+        <v>-29.75688105600001</v>
       </c>
       <c r="Q83">
-        <v>-20.68252884800001</v>
+        <v>-21.25688105600001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3855795129362998</v>
+        <v>0.4044561525438721</v>
       </c>
       <c r="T83">
-        <v>3.285927577593993</v>
+        <v>3.468479109682549</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1192712463703172</v>
+        <v>0.1178167189755572</v>
       </c>
       <c r="W83">
-        <v>0.2076758401058792</v>
+        <v>0.2080188176655636</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3727226449072414</v>
+        <v>0.3681772467986164</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2433775379436591</v>
+        <v>0.2452775379436591</v>
       </c>
       <c r="C84">
-        <v>-161.6617848179245</v>
+        <v>-166.466896008092</v>
       </c>
       <c r="D84">
-        <v>128.4122151820755</v>
+        <v>127.189103991908</v>
       </c>
       <c r="E84">
-        <v>257.124</v>
+        <v>260.706</v>
       </c>
       <c r="F84">
-        <v>293.724</v>
+        <v>297.306</v>
       </c>
       <c r="G84">
         <v>3.65</v>
@@ -8175,37 +8175,37 @@
         <v>25.5</v>
       </c>
       <c r="M84">
-        <v>69.26011920000002</v>
+        <v>70.10475480000001</v>
       </c>
       <c r="N84">
-        <v>-43.76011920000002</v>
+        <v>-44.60475480000001</v>
       </c>
       <c r="O84">
-        <v>-14.00323814400001</v>
+        <v>-14.273521536</v>
       </c>
       <c r="P84">
-        <v>-29.75688105600001</v>
+        <v>-30.33123326400001</v>
       </c>
       <c r="Q84">
-        <v>-21.25688105600001</v>
+        <v>-21.83123326400001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4044561525438721</v>
+        <v>0.425553573281747</v>
       </c>
       <c r="T84">
-        <v>3.468479109682549</v>
+        <v>3.672507292605052</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1178167189755572</v>
+        <v>0.1163972404336831</v>
       </c>
       <c r="W84">
-        <v>0.2080188176655636</v>
+        <v>0.2083535307057375</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3681772467986164</v>
+        <v>0.3637413763552597</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2452775379436591</v>
+        <v>0.2471775379436592</v>
       </c>
       <c r="C85">
-        <v>-166.466896008092</v>
+        <v>-171.2489270545151</v>
       </c>
       <c r="D85">
-        <v>127.189103991908</v>
+        <v>125.989072945485</v>
       </c>
       <c r="E85">
-        <v>260.706</v>
+        <v>264.2880000000001</v>
       </c>
       <c r="F85">
-        <v>297.306</v>
+        <v>300.8880000000001</v>
       </c>
       <c r="G85">
         <v>3.65</v>
@@ -8257,37 +8257,37 @@
         <v>25.5</v>
       </c>
       <c r="M85">
-        <v>70.10475480000001</v>
+        <v>70.94939040000003</v>
       </c>
       <c r="N85">
-        <v>-44.60475480000001</v>
+        <v>-45.44939040000003</v>
       </c>
       <c r="O85">
-        <v>-14.273521536</v>
+        <v>-14.54380492800001</v>
       </c>
       <c r="P85">
-        <v>-30.33123326400001</v>
+        <v>-30.90558547200002</v>
       </c>
       <c r="Q85">
-        <v>-21.83123326400001</v>
+        <v>-22.40558547200002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.425553573281747</v>
+        <v>0.4492881716118562</v>
       </c>
       <c r="T85">
-        <v>3.672507292605052</v>
+        <v>3.902038998392868</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1163972404336831</v>
+        <v>0.1150115589999487</v>
       </c>
       <c r="W85">
-        <v>0.2083535307057375</v>
+        <v>0.2086802743878121</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3637413763552597</v>
+        <v>0.3594111218748398</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2471775379436591</v>
+        <v>0.2490775379436591</v>
       </c>
       <c r="C86">
-        <v>-171.2489270545151</v>
+        <v>-176.0085251355326</v>
       </c>
       <c r="D86">
-        <v>125.989072945485</v>
+        <v>124.8114748644675</v>
       </c>
       <c r="E86">
-        <v>264.288</v>
+        <v>267.87</v>
       </c>
       <c r="F86">
-        <v>300.888</v>
+        <v>304.47</v>
       </c>
       <c r="G86">
         <v>3.65</v>
@@ -8339,37 +8339,37 @@
         <v>25.5</v>
       </c>
       <c r="M86">
-        <v>70.94939040000001</v>
+        <v>71.794026</v>
       </c>
       <c r="N86">
-        <v>-45.44939040000001</v>
+        <v>-46.294026</v>
       </c>
       <c r="O86">
-        <v>-14.543804928</v>
+        <v>-14.81408832</v>
       </c>
       <c r="P86">
-        <v>-30.90558547200001</v>
+        <v>-31.47993768</v>
       </c>
       <c r="Q86">
-        <v>-22.40558547200001</v>
+        <v>-22.97993768</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.449288171611856</v>
+        <v>0.4761873830526464</v>
       </c>
       <c r="T86">
-        <v>3.902038998392865</v>
+        <v>4.162174931619057</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1150115589999488</v>
+        <v>0.1136584818352435</v>
       </c>
       <c r="W86">
-        <v>0.2086802743878121</v>
+        <v>0.2089993299832496</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3594111218748399</v>
+        <v>0.3551827557351359</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2490775379436591</v>
+        <v>0.2509775379436591</v>
       </c>
       <c r="C87">
-        <v>-176.0085251355326</v>
+        <v>-180.7463134572913</v>
       </c>
       <c r="D87">
-        <v>124.8114748644675</v>
+        <v>123.6556865427088</v>
       </c>
       <c r="E87">
-        <v>267.87</v>
+        <v>271.452</v>
       </c>
       <c r="F87">
-        <v>304.47</v>
+        <v>308.052</v>
       </c>
       <c r="G87">
         <v>3.65</v>
@@ -8421,37 +8421,37 @@
         <v>25.5</v>
       </c>
       <c r="M87">
-        <v>71.794026</v>
+        <v>72.63866160000001</v>
       </c>
       <c r="N87">
-        <v>-46.294026</v>
+        <v>-47.13866160000001</v>
       </c>
       <c r="O87">
-        <v>-14.81408832</v>
+        <v>-15.084371712</v>
       </c>
       <c r="P87">
-        <v>-31.47993768</v>
+        <v>-32.054289888</v>
       </c>
       <c r="Q87">
-        <v>-22.97993768</v>
+        <v>-23.554289888</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4761873830526464</v>
+        <v>0.5069293389849782</v>
       </c>
       <c r="T87">
-        <v>4.162174931619057</v>
+        <v>4.459473141020418</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1136584818352435</v>
+        <v>0.1123368715813453</v>
       </c>
       <c r="W87">
-        <v>0.2089993299832496</v>
+        <v>0.2093109656811188</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3551827557351359</v>
+        <v>0.3510527236917041</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2509775379436591</v>
+        <v>0.2528775379436591</v>
       </c>
       <c r="C88">
-        <v>-180.7463134572913</v>
+        <v>-185.4628923535068</v>
       </c>
       <c r="D88">
-        <v>123.6556865427088</v>
+        <v>122.5211076464932</v>
       </c>
       <c r="E88">
-        <v>271.452</v>
+        <v>275.034</v>
       </c>
       <c r="F88">
-        <v>308.052</v>
+        <v>311.634</v>
       </c>
       <c r="G88">
         <v>3.65</v>
@@ -8503,37 +8503,37 @@
         <v>25.5</v>
       </c>
       <c r="M88">
-        <v>72.63866160000001</v>
+        <v>73.48329720000001</v>
       </c>
       <c r="N88">
-        <v>-47.13866160000001</v>
+        <v>-47.98329720000001</v>
       </c>
       <c r="O88">
-        <v>-15.084371712</v>
+        <v>-15.354655104</v>
       </c>
       <c r="P88">
-        <v>-32.054289888</v>
+        <v>-32.62864209600001</v>
       </c>
       <c r="Q88">
-        <v>-23.554289888</v>
+        <v>-24.12864209600001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5069293389849782</v>
+        <v>0.5424008265992073</v>
       </c>
       <c r="T88">
-        <v>4.459473141020418</v>
+        <v>4.802509536483527</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1123368715813453</v>
+        <v>0.1110456431723643</v>
       </c>
       <c r="W88">
-        <v>0.2093109656811188</v>
+        <v>0.2096154373399565</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3510527236917041</v>
+        <v>0.3470176349136386</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2528775379436591</v>
+        <v>0.2547775379436591</v>
       </c>
       <c r="C89">
-        <v>-185.4628923535068</v>
+        <v>-190.1588403252314</v>
       </c>
       <c r="D89">
-        <v>122.5211076464932</v>
+        <v>121.4071596747686</v>
       </c>
       <c r="E89">
-        <v>275.034</v>
+        <v>278.616</v>
       </c>
       <c r="F89">
-        <v>311.634</v>
+        <v>315.2160000000001</v>
       </c>
       <c r="G89">
         <v>3.65</v>
@@ -8585,37 +8585,37 @@
         <v>25.5</v>
       </c>
       <c r="M89">
-        <v>73.48329720000001</v>
+        <v>74.32793280000001</v>
       </c>
       <c r="N89">
-        <v>-47.98329720000001</v>
+        <v>-48.82793280000001</v>
       </c>
       <c r="O89">
-        <v>-15.354655104</v>
+        <v>-15.624938496</v>
       </c>
       <c r="P89">
-        <v>-32.62864209600001</v>
+        <v>-33.20299430400001</v>
       </c>
       <c r="Q89">
-        <v>-24.12864209600001</v>
+        <v>-24.70299430400001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5424008265992073</v>
+        <v>0.5837842288158079</v>
       </c>
       <c r="T89">
-        <v>4.802509536483527</v>
+        <v>5.202718664523822</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1110456431723643</v>
+        <v>0.1097837608635874</v>
       </c>
       <c r="W89">
-        <v>0.2096154373399565</v>
+        <v>0.2099129891883661</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3470176349136386</v>
+        <v>0.3430742526987108</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2547775379436591</v>
+        <v>0.2566775379436591</v>
       </c>
       <c r="C90">
-        <v>-190.1588403252314</v>
+        <v>-194.834715024412</v>
       </c>
       <c r="D90">
-        <v>121.4071596747686</v>
+        <v>120.3132849755881</v>
       </c>
       <c r="E90">
-        <v>278.616</v>
+        <v>282.198</v>
       </c>
       <c r="F90">
-        <v>315.2160000000001</v>
+        <v>318.7980000000001</v>
       </c>
       <c r="G90">
         <v>3.65</v>
@@ -8667,37 +8667,37 @@
         <v>25.5</v>
       </c>
       <c r="M90">
-        <v>74.32793280000001</v>
+        <v>75.17256840000002</v>
       </c>
       <c r="N90">
-        <v>-48.82793280000001</v>
+        <v>-49.67256840000002</v>
       </c>
       <c r="O90">
-        <v>-15.624938496</v>
+        <v>-15.89522188800001</v>
       </c>
       <c r="P90">
-        <v>-33.20299430400001</v>
+        <v>-33.77734651200001</v>
       </c>
       <c r="Q90">
-        <v>-24.70299430400001</v>
+        <v>-25.27734651200001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5837842288158079</v>
+        <v>0.6326918859808816</v>
       </c>
       <c r="T90">
-        <v>5.202718664523822</v>
+        <v>5.675693088571443</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1097837608635874</v>
+        <v>0.1085502354606258</v>
       </c>
       <c r="W90">
-        <v>0.2099129891883661</v>
+        <v>0.2102038544783844</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3430742526987108</v>
+        <v>0.3392194858144556</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2566775379436591</v>
+        <v>0.2585775379436591</v>
       </c>
       <c r="C91">
-        <v>-194.834715024412</v>
+        <v>-199.491054184752</v>
       </c>
       <c r="D91">
-        <v>120.3132849755881</v>
+        <v>119.238945815248</v>
       </c>
       <c r="E91">
-        <v>282.198</v>
+        <v>285.78</v>
       </c>
       <c r="F91">
-        <v>318.7980000000001</v>
+        <v>322.3800000000001</v>
       </c>
       <c r="G91">
         <v>3.65</v>
@@ -8749,37 +8749,37 @@
         <v>25.5</v>
       </c>
       <c r="M91">
-        <v>75.17256840000002</v>
+        <v>76.01720400000002</v>
       </c>
       <c r="N91">
-        <v>-49.67256840000002</v>
+        <v>-50.51720400000002</v>
       </c>
       <c r="O91">
-        <v>-15.89522188800001</v>
+        <v>-16.16550528000001</v>
       </c>
       <c r="P91">
-        <v>-33.77734651200001</v>
+        <v>-34.35169872000002</v>
       </c>
       <c r="Q91">
-        <v>-25.27734651200001</v>
+        <v>-25.85169872000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6326918859808816</v>
+        <v>0.6913810745789697</v>
       </c>
       <c r="T91">
-        <v>5.675693088571443</v>
+        <v>6.243262397428587</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1085502354606258</v>
+        <v>0.1073441217332855</v>
       </c>
       <c r="W91">
-        <v>0.2102038544783844</v>
+        <v>0.2104882560952913</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3392194858144556</v>
+        <v>0.3354503804165172</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2585775379436591</v>
+        <v>0.2604775379436591</v>
       </c>
       <c r="C92">
-        <v>-199.491054184752</v>
+        <v>-204.1283765031421</v>
       </c>
       <c r="D92">
-        <v>119.238945815248</v>
+        <v>118.1836234968579</v>
       </c>
       <c r="E92">
-        <v>285.78</v>
+        <v>289.362</v>
       </c>
       <c r="F92">
-        <v>322.3800000000001</v>
+        <v>325.962</v>
       </c>
       <c r="G92">
         <v>3.65</v>
@@ -8831,37 +8831,37 @@
         <v>25.5</v>
       </c>
       <c r="M92">
-        <v>76.01720400000002</v>
+        <v>76.86183960000001</v>
       </c>
       <c r="N92">
-        <v>-50.51720400000002</v>
+        <v>-51.36183960000001</v>
       </c>
       <c r="O92">
-        <v>-16.16550528000001</v>
+        <v>-16.435788672</v>
       </c>
       <c r="P92">
-        <v>-34.35169872000002</v>
+        <v>-34.92605092800001</v>
       </c>
       <c r="Q92">
-        <v>-25.85169872000002</v>
+        <v>-26.42605092800001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6913810745789697</v>
+        <v>0.7631123050877442</v>
       </c>
       <c r="T92">
-        <v>6.243262397428587</v>
+        <v>6.936958219365097</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1073441217332855</v>
+        <v>0.1061645159999527</v>
       </c>
       <c r="W92">
-        <v>0.2104882560952913</v>
+        <v>0.2107664071272112</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3354503804165172</v>
+        <v>0.3317641124998523</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2604775379436591</v>
+        <v>0.2623775379436591</v>
       </c>
       <c r="C93">
-        <v>-204.1283765031421</v>
+        <v>-208.7471824746942</v>
       </c>
       <c r="D93">
-        <v>118.1836234968579</v>
+        <v>117.1468175253058</v>
       </c>
       <c r="E93">
-        <v>289.362</v>
+        <v>292.944</v>
       </c>
       <c r="F93">
-        <v>325.962</v>
+        <v>329.544</v>
       </c>
       <c r="G93">
         <v>3.65</v>
@@ -8913,37 +8913,37 @@
         <v>25.5</v>
       </c>
       <c r="M93">
-        <v>76.86183960000001</v>
+        <v>77.70647520000001</v>
       </c>
       <c r="N93">
-        <v>-51.36183960000001</v>
+        <v>-52.20647520000001</v>
       </c>
       <c r="O93">
-        <v>-16.435788672</v>
+        <v>-16.706072064</v>
       </c>
       <c r="P93">
-        <v>-34.92605092800001</v>
+        <v>-35.50040313600001</v>
       </c>
       <c r="Q93">
-        <v>-26.42605092800001</v>
+        <v>-27.00040313600001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7631123050877442</v>
+        <v>0.8527763432237124</v>
       </c>
       <c r="T93">
-        <v>6.936958219365097</v>
+        <v>7.804077996785737</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1061645159999527</v>
+        <v>0.1050105538695184</v>
       </c>
       <c r="W93">
-        <v>0.2107664071272112</v>
+        <v>0.2110385113975676</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3317641124998523</v>
+        <v>0.3281579808422451</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2623775379436591</v>
+        <v>0.2642775379436591</v>
       </c>
       <c r="C94">
-        <v>-208.7471824746942</v>
+        <v>-213.3479551842048</v>
       </c>
       <c r="D94">
-        <v>117.1468175253058</v>
+        <v>116.1280448157952</v>
       </c>
       <c r="E94">
-        <v>292.944</v>
+        <v>296.526</v>
       </c>
       <c r="F94">
-        <v>329.544</v>
+        <v>333.126</v>
       </c>
       <c r="G94">
         <v>3.65</v>
@@ -8995,37 +8995,37 @@
         <v>25.5</v>
       </c>
       <c r="M94">
-        <v>77.70647520000001</v>
+        <v>78.55111080000002</v>
       </c>
       <c r="N94">
-        <v>-52.20647520000001</v>
+        <v>-53.05111080000002</v>
       </c>
       <c r="O94">
-        <v>-16.706072064</v>
+        <v>-16.97635545600001</v>
       </c>
       <c r="P94">
-        <v>-35.50040313600001</v>
+        <v>-36.07475534400001</v>
       </c>
       <c r="Q94">
-        <v>-27.00040313600001</v>
+        <v>-27.57475534400001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8527763432237124</v>
+        <v>0.9680586779699571</v>
       </c>
       <c r="T94">
-        <v>7.804077996785737</v>
+        <v>8.918946282040842</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1050105538695184</v>
+        <v>0.103881408128986</v>
       </c>
       <c r="W94">
-        <v>0.2110385113975676</v>
+        <v>0.2113047639631851</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3281579808422451</v>
+        <v>0.3246294004030812</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2642775379436591</v>
+        <v>0.2661775379436591</v>
       </c>
       <c r="C95">
-        <v>-213.3479551842048</v>
+        <v>-217.9311610566764</v>
       </c>
       <c r="D95">
-        <v>116.1280448157952</v>
+        <v>115.1268389433237</v>
       </c>
       <c r="E95">
-        <v>296.526</v>
+        <v>300.1080000000001</v>
       </c>
       <c r="F95">
-        <v>333.126</v>
+        <v>336.7080000000001</v>
       </c>
       <c r="G95">
         <v>3.65</v>
@@ -9077,37 +9077,37 @@
         <v>25.5</v>
       </c>
       <c r="M95">
-        <v>78.55111080000002</v>
+        <v>79.39574640000002</v>
       </c>
       <c r="N95">
-        <v>-53.05111080000002</v>
+        <v>-53.89574640000002</v>
       </c>
       <c r="O95">
-        <v>-16.97635545600001</v>
+        <v>-17.24663884800001</v>
       </c>
       <c r="P95">
-        <v>-36.07475534400001</v>
+        <v>-36.64910755200002</v>
       </c>
       <c r="Q95">
-        <v>-27.57475534400001</v>
+        <v>-28.14910755200002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9680586779699571</v>
+        <v>1.121768457631617</v>
       </c>
       <c r="T95">
-        <v>8.918946282040842</v>
+        <v>10.40543732904765</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.103881408128986</v>
+        <v>0.1027762867659117</v>
       </c>
       <c r="W95">
-        <v>0.2113047639631851</v>
+        <v>0.211565351580598</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3246294004030812</v>
+        <v>0.321175896143474</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2661775379436591</v>
+        <v>0.2680775379436591</v>
       </c>
       <c r="C96">
-        <v>-217.9311610566764</v>
+        <v>-222.4972505693457</v>
       </c>
       <c r="D96">
-        <v>115.1268389433237</v>
+        <v>114.1427494306543</v>
       </c>
       <c r="E96">
-        <v>300.1080000000001</v>
+        <v>303.6900000000001</v>
       </c>
       <c r="F96">
-        <v>336.7080000000001</v>
+        <v>340.2900000000001</v>
       </c>
       <c r="G96">
         <v>3.65</v>
@@ -9159,37 +9159,37 @@
         <v>25.5</v>
       </c>
       <c r="M96">
-        <v>79.39574640000002</v>
+        <v>80.24038200000003</v>
       </c>
       <c r="N96">
-        <v>-53.89574640000002</v>
+        <v>-54.74038200000003</v>
       </c>
       <c r="O96">
-        <v>-17.24663884800001</v>
+        <v>-17.51692224000001</v>
       </c>
       <c r="P96">
-        <v>-36.64910755200002</v>
+        <v>-37.22345976000001</v>
       </c>
       <c r="Q96">
-        <v>-28.14910755200002</v>
+        <v>-28.72345976000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.121768457631617</v>
+        <v>1.336962149157941</v>
       </c>
       <c r="T96">
-        <v>10.40543732904765</v>
+        <v>12.48652479485719</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1027762867659117</v>
+        <v>0.1016944311157442</v>
       </c>
       <c r="W96">
-        <v>0.211565351580598</v>
+        <v>0.2118204531429075</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.321175896143474</v>
+        <v>0.3177950972367005</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2680775379436591</v>
+        <v>0.2699775379436591</v>
       </c>
       <c r="C97">
-        <v>-222.4972505693457</v>
+        <v>-227.046658927505</v>
       </c>
       <c r="D97">
-        <v>114.1427494306543</v>
+        <v>113.1753410724951</v>
       </c>
       <c r="E97">
-        <v>303.6900000000001</v>
+        <v>307.272</v>
       </c>
       <c r="F97">
-        <v>340.2900000000001</v>
+        <v>343.8720000000001</v>
       </c>
       <c r="G97">
         <v>3.65</v>
@@ -9241,37 +9241,37 @@
         <v>25.5</v>
       </c>
       <c r="M97">
-        <v>80.24038200000003</v>
+        <v>81.08501760000001</v>
       </c>
       <c r="N97">
-        <v>-54.74038200000003</v>
+        <v>-55.58501760000001</v>
       </c>
       <c r="O97">
-        <v>-17.51692224000001</v>
+        <v>-17.78720563200001</v>
       </c>
       <c r="P97">
-        <v>-37.22345976000001</v>
+        <v>-37.797811968</v>
       </c>
       <c r="Q97">
-        <v>-28.72345976000001</v>
+        <v>-29.297811968</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.336962149157941</v>
+        <v>1.659752686447427</v>
       </c>
       <c r="T97">
-        <v>12.48652479485719</v>
+        <v>15.60815599357149</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1016944311157442</v>
+        <v>0.1006351141249552</v>
       </c>
       <c r="W97">
-        <v>0.2118204531429075</v>
+        <v>0.2120702400893356</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3177950972367005</v>
+        <v>0.314484731640485</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2699775379436591</v>
+        <v>0.2718775379436591</v>
       </c>
       <c r="C98">
-        <v>-227.0466589275049</v>
+        <v>-231.5798067062432</v>
       </c>
       <c r="D98">
-        <v>113.1753410724951</v>
+        <v>112.2241932937568</v>
       </c>
       <c r="E98">
-        <v>307.272</v>
+        <v>310.854</v>
       </c>
       <c r="F98">
-        <v>343.872</v>
+        <v>347.454</v>
       </c>
       <c r="G98">
         <v>3.65</v>
@@ -9323,37 +9323,37 @@
         <v>25.5</v>
       </c>
       <c r="M98">
-        <v>81.0850176</v>
+        <v>81.9296532</v>
       </c>
       <c r="N98">
-        <v>-55.5850176</v>
+        <v>-56.4296532</v>
       </c>
       <c r="O98">
-        <v>-17.787205632</v>
+        <v>-18.057489024</v>
       </c>
       <c r="P98">
-        <v>-37.797811968</v>
+        <v>-38.372164176</v>
       </c>
       <c r="Q98">
-        <v>-29.297811968</v>
+        <v>-29.872164176</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.659752686447423</v>
+        <v>2.19773691526323</v>
       </c>
       <c r="T98">
-        <v>15.60815599357145</v>
+        <v>20.81087465809527</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1006351141249552</v>
+        <v>0.09959763872160514</v>
       </c>
       <c r="W98">
-        <v>0.2120702400893356</v>
+        <v>0.2123148767894455</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.314484731640485</v>
+        <v>0.311242621005016</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2718775379436591</v>
+        <v>0.2737775379436591</v>
       </c>
       <c r="C99">
-        <v>-231.5798067062432</v>
+        <v>-236.0971004600991</v>
       </c>
       <c r="D99">
-        <v>112.2241932937568</v>
+        <v>111.288899539901</v>
       </c>
       <c r="E99">
-        <v>310.854</v>
+        <v>314.436</v>
       </c>
       <c r="F99">
-        <v>347.454</v>
+        <v>351.0360000000001</v>
       </c>
       <c r="G99">
         <v>3.65</v>
@@ -9405,37 +9405,37 @@
         <v>25.5</v>
       </c>
       <c r="M99">
-        <v>81.9296532</v>
+        <v>82.77428880000002</v>
       </c>
       <c r="N99">
-        <v>-56.4296532</v>
+        <v>-57.27428880000002</v>
       </c>
       <c r="O99">
-        <v>-18.057489024</v>
+        <v>-18.32777241600001</v>
       </c>
       <c r="P99">
-        <v>-38.372164176</v>
+        <v>-38.94651638400001</v>
       </c>
       <c r="Q99">
-        <v>-29.872164176</v>
+        <v>-30.44651638400001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.19773691526323</v>
+        <v>3.273705372894845</v>
       </c>
       <c r="T99">
-        <v>20.81087465809527</v>
+        <v>31.21631198714291</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09959763872160514</v>
+        <v>0.09858133628567035</v>
       </c>
       <c r="W99">
-        <v>0.2123148767894455</v>
+        <v>0.2125545209038389</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.311242621005016</v>
+        <v>0.3080666758927199</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2737775379436591</v>
+        <v>0.2756775379436591</v>
       </c>
       <c r="C100">
-        <v>-236.0971004600991</v>
+        <v>-240.5989333024781</v>
       </c>
       <c r="D100">
-        <v>111.288899539901</v>
+        <v>110.3690666975219</v>
       </c>
       <c r="E100">
-        <v>314.436</v>
+        <v>318.018</v>
       </c>
       <c r="F100">
-        <v>351.0360000000001</v>
+        <v>354.6180000000001</v>
       </c>
       <c r="G100">
         <v>3.65</v>
@@ -9487,37 +9487,37 @@
         <v>25.5</v>
       </c>
       <c r="M100">
-        <v>82.77428880000002</v>
+        <v>83.61892440000001</v>
       </c>
       <c r="N100">
-        <v>-57.27428880000002</v>
+        <v>-58.11892440000001</v>
       </c>
       <c r="O100">
-        <v>-18.32777241600001</v>
+        <v>-18.59805580800001</v>
       </c>
       <c r="P100">
-        <v>-38.94651638400001</v>
+        <v>-39.52086859200001</v>
       </c>
       <c r="Q100">
-        <v>-30.44651638400001</v>
+        <v>-31.02086859200001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.273705372894845</v>
+        <v>6.50161074578969</v>
       </c>
       <c r="T100">
-        <v>31.21631198714291</v>
+        <v>62.4326239742858</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09858133628567035</v>
+        <v>0.09758556521207774</v>
       </c>
       <c r="W100">
-        <v>0.2125545209038389</v>
+        <v>0.2127893237229921</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3080666758927199</v>
+        <v>0.304954891287743</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2756775379436591</v>
-      </c>
-      <c r="C101">
-        <v>-240.5989333024781</v>
-      </c>
-      <c r="D101">
-        <v>110.3690666975219</v>
-      </c>
-      <c r="E101">
-        <v>318.018</v>
-      </c>
-      <c r="F101">
-        <v>354.6180000000001</v>
-      </c>
-      <c r="G101">
-        <v>3.65</v>
-      </c>
-      <c r="H101">
-        <v>321.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>34</v>
-      </c>
-      <c r="K101">
-        <v>8.5</v>
-      </c>
-      <c r="L101">
-        <v>25.5</v>
-      </c>
-      <c r="M101">
-        <v>83.61892440000001</v>
-      </c>
-      <c r="N101">
-        <v>-58.11892440000001</v>
-      </c>
-      <c r="O101">
-        <v>-18.59805580800001</v>
-      </c>
-      <c r="P101">
-        <v>-39.52086859200001</v>
-      </c>
-      <c r="Q101">
-        <v>-31.02086859200001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.50161074578969</v>
-      </c>
-      <c r="T101">
-        <v>62.4326239742858</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09758556521207774</v>
-      </c>
-      <c r="W101">
-        <v>0.2127893237229921</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.304954891287743</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
